--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run - only the 12-month path was driven.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: selecting Last 3 Months redrew the chart with exactly 3 month labels.</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: selecting Last 24 Months redrew the chart with exactly 24 month labels spanning two years.</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Paymentus account exists in credentials/qa.json - cannot be run on QA today.</t>
+          <t xml:space="preserve">QA 2026-09-15 Paymentus: legend read ['Ach','Token','Card'] - the only gateway showing all three series.</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Paymentus account available.</t>
+          <t xml:space="preserve">QA 2026-09-15 Paymentus: tooltip showed Ach(29), Token(246) and Card(63) together.</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised - hover tooltip not driven in this run.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: tooltip read Token(3) and Card(52); the summary cards for the same month read Token (3) and Card (52) - identical.</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised - only one bar was clicked in this run.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: clicking a different bar replaced the heading with the new month and reset the table footer to '1-15 of 36', confirming the paging reset.</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Paymentus account available.</t>
+          <t xml:space="preserve">QA 2026-09-15 Paymentus: CONFIRMED. Two POSTs fired - the first with page_size 15, the second automatically with page_size 198 matching totalRecord, so the summary counts cover the whole month.</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Paymentus account available.</t>
+          <t xml:space="preserve">QA 2026-09-15 Paymentus: all three cards rendered - Ach (29), Token (246), Card (63) - each with a currency-formatted value.</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14 SnapPay Apr 2026: 3 + 52 = 55 and the table footer read '1-15 of 55'. Counts reconcile. Written against Paymentus but the reconciliation held on SnapPay.</t>
+          <t xml:space="preserve">QA 2026-09-15 Paymentus: card counts matched the tooltip exactly for the same month (29 / 246 / 63). Note the drill-down table holds 198 rows because it is filtered to Sale requests, so it is not expected to equal the sum of the cards.</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14 SnapPay: all four controls present (first / previous / next / last page). Paging itself not driven.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: the next-page control moved the footer from '1-15 of 55' to '16-30 of 55'. First/previous/last were present but only next was driven.</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       <c r="N46" s="2"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: switching rows per page from 15 to 25 re-rendered 25 rows, moved the footer to '1-25 of 55' and sent page_size 25.</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       <c r="N47" s="2"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised - the duplicate-request question is still open.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: from page 2 ('26-50 of 55') switching back to 15 returned the table AND the pagination control to page 1 ('1-15 of 55'). Confirmed the duplicate-request behaviour - the single action fired TWO transaction POSTs, both with page_number 1.</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       <c r="N49" s="2"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14 SnapPay: timestamps rendered as '4/30/2026, 11:30:39 AM' but no cross-check against the Transactions module was done.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: timestamps render in the viewer's locale format (e.g. '4/30/2026, 11:30:39 AM'). The conversion against a different profile timezone was not cross-checked, so treat the timezone half as unproven.</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       <c r="N50" s="2"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised - download not triggered in this run.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: 'Export to Excel' downloaded a file named Transactions.xls.</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       <c r="N51" s="2"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: 'Export to Pdf' downloaded a file named paymentTrendsTable.pdf.</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5212,7 @@
       <c r="N52" s="2"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: with 25 rows on screen the exported file contained exactly 25 data rows - the export covers the current page only, not the whole month.</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5408,7 @@
       <c r="N54" s="2"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: clicking refresh issued a fresh periodic_payment_stats_us request and the chart redrew.</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       <c r="N55" s="2"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: the refresh request carried the same pageSize as the selected range, so the range is preserved.</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       <c r="N56" s="2"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised - still worth confirming with the product owner.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: CONFIRMED - the drill-down was still open after refresh. Only changing the time range clears it. Confirm with the product owner whether that is intended.</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: corrupting the stored token and forcing a refresh did NOT redirect to sign-in - the page stayed on /paymenttrends and the corrupted token remained in storage. It is not clear whether a request was actually made, so this is inconclusive rather than a confirmed failure. Re-test by letting a session expire naturally.</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: ANOMALY WORTH CHECKING MANUALLY. Clicking three different bars in quick succession left the drill-down showing the FIRST month clicked (Apr 2026), not the last. That is the stale-response risk this case is meant to catch, but the clicks were script-driven at speed and the later ones may have landed on shifted layout. Re-run this one by hand before raising it.</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7282,7 @@
       <c r="N73" s="2"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrected after run</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: CORRECTED - observed From Date 08/15/2026 12:00 AM against a To Date of 09/14/2026, i.e. today minus 30 days, NOT the 1st of the previous month. The module doc and my original case were both wrong.</t>
+          <t xml:space="preserve">QA 2026-09-15: re-confirmed on a second day - defaults read 08/16/2026 to 09/15/2026, exactly 30 days, not the 1st of the previous month.</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       <c r="N80" s="2"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised - date validation not driven in this run.</t>
+          <t xml:space="preserve">QA 2026-09-15 IPG: setting To Date earlier than From Date and pressing Submit produced the message 'Invalid date range' and fired zero stats requests.</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
       <c r="N81" s="2"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 IPG: setting From Date to a future date and pressing Submit fired zero stats requests and produced NO message of any kind - the silent rejection is confirmed, and it is inconsistent with the inverted-range case above.</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       <c r="N82" s="2"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised - calendar constraints are set in code but were not clicked through.</t>
+          <t xml:space="preserve">QA 2026-09-15 IPG: opening the From calendar and stepping to the current month showed 18 disabled days against 17 enabled - future dates are blocked. Navigation past the current month was also refused.</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       <c r="N83" s="2"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 IPG: the To calendar opened on the current month; stepping back to the From month showed 21 disabled days against 21 enabled - dates before the selected From Date are blocked.</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8660,7 @@
       <c r="N87" s="2"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 IPG: clearing the From field left the placeholder showing and pressing Submit fired ZERO stats requests, so no blank range reaches the API.</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       <c r="N88" s="2"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Corrected after run</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 IPG: CORRECTED - typing '13/45/2026 99:99 XX' is not rejected. The picker coerces it to a valid date (observed '03/04/2026 09:09 AM') and Submit then fires a normal request. The original expectation of 'no request is sent' was wrong; the page stays stable, which is the real point.</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       <c r="N93" s="2"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: the refresh icon's class changed on click, confirming the animation is applied. The exact spin class was not captured because it clears after about a second.</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
       <c r="N94" s="2"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: clicking the refresh icon collapsed the expanded Prepare Query panel.</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       <c r="N96" s="2"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: three rapid Submit clicks produced three stats requests - there is no debouncing. The table stayed consistent with the selected range. Watch for a slow earlier response overwriting a newer one on a loaded environment.</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised - header clicks not driven.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: clicking a column header changed nothing and no sort arrow appeared - but the grid was empty because of the page-wide 400, so this proves little. Re-test once PS-NEG-11 is fixed.</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       <c r="N107" s="2"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised - panel not expanded in this run.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: panel was collapsed on load, expanded on click, and showed Select, Group, Having, And/Or, Execute and Cancel. 'Having 1' stays hidden until And/Or is chosen.</t>
         </is>
       </c>
     </row>
@@ -10723,7 +10723,7 @@
       <c r="N108" s="2"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: Select opened pre-populated with Funding Method, Funding Category, Channel and Displayed Fee Amount - and Group carries the same four by default.</t>
         </is>
       </c>
     </row>
@@ -10820,7 +10820,7 @@
       <c r="N109" s="2"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: Select opened pre-populated with exactly Request Type, Channel, transaction Amount and Fee Amount.</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       <c r="N110" s="2"/>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: removing every Select chip left 0 chips and the Execute button became disabled.</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       <c r="N111" s="2"/>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: clearing every Group chip left 0 chips, disabled the Having controls and disabled Execute.</t>
         </is>
       </c>
     </row>
@@ -11114,7 +11114,7 @@
       <c r="N112" s="2"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: Having field options were exactly Funding Method, Funding Category, Channel, Displayed Fee Amount; choosing the text field 'Funding Method' offered exactly two operators - 'is equal to' and 'is not equal to'.</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       <c r="N113" s="2"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="S113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: choosing the amount field 'Displayed Fee Amount' offered all six operators - is equal to, is not equal to, is greater than, is greater than and equal to, is less than, is less than and equal to.</t>
         </is>
       </c>
     </row>
@@ -11310,7 +11310,7 @@
       <c r="N114" s="2"/>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="S114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: the And/Or control was disabled while the first Having row was incomplete.</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="S119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised, but the default query params were confirmed per gateway: IPG request_type; SnapPay request_type,channel,transaction_amount,fee_amount; CommerceHub payment_type; BillPay funding_method,funding_category,channel,displayed_fee_amount.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: pressing Execute with the DEFAULT chips sent select_fields and groupby_fields identically as 'request_type,channel,transaction_amount,fee_amount' - no mismatch on this path. The risk only arises if the amount field is removed and re-added from the Select dropdown, which re-reads a different option list. Re-test by removing and re-adding 'transaction Amount' before pressing Execute.</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       <c r="N126" s="2"/>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="S126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Console output not captured in this run - worth doing while the 400 is still reproducible.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: CONFIRMED - the browser console shows 'err is not defined' alongside the 400. The failure handler throws its own ReferenceError, so the real API error never reaches the console. Also seen: repeated 'Invalid value used as weak map key' page errors.</t>
         </is>
       </c>
     </row>
@@ -13262,7 +13262,7 @@
       <c r="N134" s="2"/>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="S134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: navigating to Payment Trends and back reset the From Date to the default 30-day window and left the Prepare Query panel collapsed - a clean state with no leftovers.</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="S137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not executed. These create real payments on the shared QA environment, which needs your go-ahead first. The Payment Stats half is also blocked until PS-NEG-11 is fixed - with sub_merchant_id sent empty the page returns 400 and shows no figures to compare against.</t>
+          <t xml:space="preserve">QA 2026-09-15: the payment half of this flow is proven (see PA-E2E-03) and Virtual Terminal is a valid entry point - the payment is recorded as a 'Sale' request type and is picked up by the analytics filters. The Payment Stats half still cannot be checked while PS-NEG-11 leaves that page returning 400 with no figures.</t>
         </is>
       </c>
     </row>
@@ -13765,7 +13765,7 @@
       <c r="N139" s="2"/>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P139" s="2" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="S139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not executed. These create real payments on the shared QA environment, which needs your go-ahead first. The Payment Stats half is also blocked until PS-NEG-11 is fixed - with sub_merchant_id sent empty the page returns 400 and shows no figures to compare against.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: CONFIRMED end to end. Current-month tooltip read Token(12) Card(45) before the payment; a card payment was taken through Virtual Terminal &gt; Collect Payment; after refreshing, the same month read Token(12) Card(46) - the card count rose by exactly one and the token count did not move.</t>
         </is>
       </c>
     </row>
@@ -13865,7 +13865,7 @@
       <c r="N140" s="2"/>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="S140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not executed. These create real payments on the shared QA environment, which needs your go-ahead first. The Payment Stats half is also blocked until PS-NEG-11 is fixed - with sub_merchant_id sent empty the page returns 400 and shows no figures to compare against.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: CONFIRMED. The new payment appeared on page 1 of the drill-down as request type 'CardSale' with the correct amount, the customer number used at payment time, a timestamp within a minute of the payment, and status SUCCESS. The footer total also rose by one.</t>
         </is>
       </c>
     </row>
@@ -14460,7 +14460,7 @@
       <c r="N146" s="2"/>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="S146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not executed. These create real payments on the shared QA environment, which needs your go-ahead first. The Payment Stats half is also blocked until PS-NEG-11 is fixed - with sub_merchant_id sent empty the page returns 400 and shows no figures to compare against.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: CONFIRMED. 'Export to Excel' produced Transactions.xls and the newly created payment was present in the exported rows.</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="S149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not executed. These create real payments on the shared QA environment, which needs your go-ahead first. The Payment Stats half is also blocked until PS-NEG-11 is fixed - with sub_merchant_id sent empty the page returns 400 and shows no figures to compare against.</t>
+          <t xml:space="preserve">QA 2026-09-15: single-payment aggregation is proven by PA-E2E-03 (+1 exactly). The multi-payment sum still needs the Payment Stats amount column, which is blocked by PS-NEG-11.</t>
         </is>
       </c>
     </row>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">91</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -7596,7 +7596,7 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -8875,7 +8875,7 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 BillPay: clicking a column header changed nothing and no sort arrow appeared - but the grid was empty because of the page-wide 400, so this proves little. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: clicking a column header changed nothing and no sort arrow appeared - but the grid was empty because I had opened the page by URL, which drops the sub-merchant id (PS-NEG-11). Re-test by reaching Payment Stats from the sidebar so the table has rows to sort.</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="S115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="S117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="S121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -12112,7 +12112,7 @@
       </c>
       <c r="S122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -12305,7 +12305,7 @@
       </c>
       <c r="S124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12698,7 @@
       </c>
       <c r="S128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="S129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -12893,7 +12893,7 @@
       </c>
       <c r="S130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="S131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="S133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: blocked by the page-wide 400 - payment_stats_us is rejected for every gateway because sub_merchant_id is sent empty, so no data ever renders. Re-test once PS-NEG-11 is fixed.</t>
+          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
         </is>
       </c>
     </row>
@@ -13307,35 +13307,37 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stats request must carry the active sub-merchant identifier</t>
+          <t xml:space="preserve">Payment Stats keeps its data after a page refresh</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Network tab open</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Network tab open, filtered on payment_stats</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every payment_stats_us call must include a populated sub_merchant_id
-The backend rejects the call outright when it is missing
+          <t xml:space="preserve">Reach the page two ways and compare:
+  (a) click Payment Analytics &gt; Payment Stats in the sidebar
+  (b) press F5 on that same page, or paste the /paymentStats URL into a fresh tab
+Watch the sub_merchant_id query parameter on each request
 Gateway: any - behaviour is identical on every gateway</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open DevTools &gt; Network and filter on payment_stats
-2. Navigate to Payment Stats
-3. Inspect the outgoing request query string
-4. Find the sub_merchant_id parameter
-5. Verify it carries the identifier of the sub-merchant selected in the portal header, and is not blank
-6. Verify the response is HTTP 200 and the table populates
-7. Repeat for IPG, BillPay, SnapPay, CommerceHub, MerchantE and NuveiPaya</t>
+          <t xml:space="preserve">1. Log in and open DevTools &gt; Network, filtering on 'payment_stats'
+2. Navigate to Payment Analytics &gt; Payment Stats using the sidebar
+3. Inspect the payment_stats_us request and verify sub_merchant_id carries the id shown in the portal header
+4. Verify the response is 200 and the table renders its payment-type rows
+5. Now press F5 to refresh that same page
+6. Inspect the new payment_stats_us request and verify sub_merchant_id is still populated
+7. Verify the response is still 200 and the table still shows its rows</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sub_merchant_id must be populated on every request and the call must return 200 with data. A blank value makes the backend reject the call and leaves the page permanently empty (defect, log it)</t>
+          <t xml:space="preserve">The page must load its data whichever way it is reached. A refresh that sends an empty sub_merchant_id, returns 400 and empties the table - with no error shown to the user - is a defect (log it)</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -13381,7 +13383,7 @@
       </c>
       <c r="S135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: CONFIRMED and this is the headline defect. sub_merchant_id was sent EMPTY on every payment_stats_us request for IPG, BillPay, SnapPay and CommerceHub, and the backend rejects it with HTTP 400 ('sub_merchant_id is required'). Payment Stats therefore shows no data for any gateway on QA. Root cause: the mount effect fires the request before the sub-merchant is known and marks the range as already set, which permanently blocks the follow-up effect that would have re-fetched with a valid id.</t>
+          <t xml:space="preserve">QA 2026-09-14: CONFIRMED, and the trigger is a page refresh - NOT every request as first recorded. Navigating to Payment Stats from the sidebar sends a populated sub_merchant_id and the table renders normally. Pressing F5 on that same page re-sends it EMPTY, the backend returns 400 and the table empties with no error shown. Confirmed independently by the user in a normal browser session.</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13586,7 @@
       </c>
       <c r="S137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15: the payment half of this flow is proven (see PA-E2E-03) and Virtual Terminal is a valid entry point - the payment is recorded as a 'Sale' request type and is picked up by the analytics filters. The Payment Stats half still cannot be checked while PS-NEG-11 leaves that page returning 400 with no figures.</t>
+          <t xml:space="preserve">QA 2026-09-15: the payment half of this flow is proven (see PA-E2E-03) and Virtual Terminal is a valid entry point - the payment is recorded as a 'Sale' request type and is picked up by the analytics filters. The Payment Stats half is testable by navigating from the sidebar - just do not refresh the page, see PS-NEG-11.</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14782,7 @@
       </c>
       <c r="S149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15: single-payment aggregation is proven by PA-E2E-03 (+1 exactly). The multi-payment sum still needs the Payment Stats amount column, which is blocked by PS-NEG-11.</t>
+          <t xml:space="preserve">QA 2026-09-15: single-payment aggregation is proven by PA-E2E-03 (+1 exactly). The multi-payment sum needs the Payment Stats amount column, which renders fine when the page is reached from the sidebar.</t>
         </is>
       </c>
     </row>
@@ -15792,7 +15794,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Payment Stats is broken for every gateway</t>
+          <t xml:space="preserve">Payment Stats loses its data on refresh</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -15802,7 +15804,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sub_merchant_id sent empty on every request; backend returns 400</t>
+          <t xml:space="preserve">reached from the sidebar it works; a refresh or direct URL sends an empty sub_merchant_id and returns 400</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15821,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the 400 produces no toast, no banner, no message</t>
+          <t xml:space="preserve">the refresh 400 produces no toast, no banner, no message - it looks like a merchant with no payments</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -9710,12 +9710,13 @@
 6. Verify 'Qty'
 7. Verify 'Qty(%)'
 8. Repeat steps 1 to 7 as a CommerceHub merchant
-9. Repeat steps 1 to 7 as a NuveiPaya merchant</t>
+9. Repeat steps 1 to 7 as a NuveiPaya merchant
+10. Note: the columns need not appear in any particular order — only that all five are present</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">All three standard gateways show exactly Type, Amount, Amount(%), Qty and Qty(%) in that order</t>
+          <t xml:space="preserve">All three standard gateways show all five columns — Type, Amount, Amount(%), Qty and Qty(%). Column order is not asserted: reordering them changes nothing for the merchant</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -9819,7 +9820,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BillPay shows exactly those six columns in that order - a completely different set from IPG</t>
+          <t xml:space="preserve">BillPay shows all six columns — a completely different set from IPG. Order is not asserted: reordering them changes nothing for the merchant</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -9922,7 +9923,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SnapPay shows exactly those five columns in that order</t>
+          <t xml:space="preserve">SnapPay shows all five columns. Order is not asserted</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -10783,40 +10783,49 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every month bar drills down and reconciles with the Transactions module</t>
+          <t xml:space="preserve">Every month bar drills down and reconciles for count and amount</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MerchantE customer-portal user authenticated; Payment Analytics group visible in sidebar; Payment Trends page reachable; Transactions module accessible for the same merchant</t>
+          <t xml:space="preserve">MerchantE customer-portal user authenticated; Payment Analytics group visible in sidebar; Payment Trends page reachable; Transactions module accessible for the same merchant; DevTools Network tab open</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk EVERY bar in the chart, not just one
-Compare per month: transaction count AND total amount
-Transactions filter: date between the 1st and last day of that month, plus the authorised/successful status for that gateway (BillPay: Authorization Status = Authorized)
+          <t xml:space="preserve">Walk EVERY bar in the chart, not just one.
+Where each figure comes from:
+  COUNT  - read from the UI. The screen is the only place it is shown: the hover tooltip,
+           the number in brackets on each summary card, and the table footer total.
+  AMOUNT - read from the periodic_payment_stats_us response. There is NO month total on
+           screen, so take the per-type amounts from the response for the selected month:
+             sumOfSuccessCardPayment  -&gt; the card amount
+             sumOfSuccessAchPayment   -&gt; the ACH amount
+Transactions filter: date between the 1st and last day of that month, plus the authorised/
+successful status for that gateway (BillPay: Authorization Status = Authorized)
 Gateway: any - behaviour is identical on every gateway</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Payment Trends with the default Last 6 Months range
-2. Take the left-most bar first, then work across to the right
-3. Hover the bar and note the counts shown in the tooltip
-4. Click it and verify 'Selected Month' names that same month
-5. Note the count in brackets on each summary card, and the amount beneath it
-6. Note the record total in the transaction table footer
-7. Open the Transactions module and filter to that month with the authorised status
-8. Verify the transaction count there matches the drill-down footer total
-9. Verify the total amount there matches the sum of the summary card amounts
-10. Repeat steps 3 to 9 for every remaining bar in the chart
-11. Verify a month whose bar has no height opens an empty drill-down rather than an error</t>
+          <t xml:space="preserve">1. Open DevTools &gt; Network and filter on 'periodic', then open Payment Trends
+2. Keep the periodic_payment_stats_us response open - it carries one entry per month
+3. Take the left-most bar first, then work across to the right
+4. Hover the bar and note the Card and ACH counts from the tooltip
+5. Click the bar and verify 'Selected Month' names that same month
+6. Note the count in brackets on each summary card, and the record total in the table footer
+7. In the response, find that month's entry and read sumOfSuccessCardPayment and sumOfSuccessAchPayment
+8. Open the Transactions module and filter to that month with the authorised status
+9. Verify the transaction count there matches the count shown on screen for that month
+10. Verify the card total there matches sumOfSuccessCardPayment for that month
+11. Verify the ACH total there matches sumOfSuccessAchPayment for that month
+12. Repeat steps 4 to 11 for every remaining bar in the chart
+13. Verify a month whose bar has no height opens an empty drill-down rather than an error</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every month in the range drills down to its own figures, and both the count and the amount match the Transactions module for that month. One month disagreeing while the others match points at that month's data rather than the page (log it with the month named)</t>
+          <t xml:space="preserve">For every month in the range: the count on screen matches the Transactions module, and the card and ACH amounts in the periodic stats response match the same totals there. One month disagreeing while the others match points at that month's data rather than the page (log it with the month named)</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -10847,7 +10856,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">@PaymentAnalytics @PaymentTrends @allGateways @dataintegrity @regression</t>
+          <t xml:space="preserve">@PaymentAnalytics @PaymentTrends @allGateways @api @dataintegrity @regression</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -6135,38 +6135,44 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Browser console shows a secondary error when the stats request fails</t>
+          <t xml:space="preserve">Failure handler hides the real API error when a stats request fails</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Console open; ability to fail the stats request</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Console open; ability to block or fail the stats request</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The failure handler itself throws, masking the original error
+          <t xml:space="preserve">This only shows up on a FAILED request. A healthy session never enters the failure handler,
+so the console stays clean apart from unrelated page noise ('Invalid value used as weak map key',
+which appears on every page regardless).
+To see it you must make the stats call fail - block payment_stats_us in DevTools, or use a
+merchant whose record is broken.
 Gateway: any - behaviour is identical on every gateway</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open DevTools &gt; Console and clear it
-2. Block the payment_stats_us request
-3. Navigate to Payment Stats and let the request fail
-4. Read the console output
-5. Verify whether the real API error is logged
-6. Note any reference error raised by the handler itself instead of the underlying cause</t>
+2. Open Payment Stats normally first and confirm the console shows no reference error - this is
+   the control, and proves the next step is caused by the failure and not by the page itself
+3. Now block the payment_stats_us request in DevTools
+4. Reload Payment Stats and let the request fail
+5. Read the console output
+6. Verify the real API error reaches the console
+7. Note any reference error thrown by the handler itself in place of the underlying cause</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The genuine API error should reach the console. A handler that throws its own error and hides the real cause makes support diagnosis impossible (defect, log it)</t>
+          <t xml:space="preserve">When a stats request fails, the genuine API error must reach the console. A handler that throws its own reference error and swallows the real cause leaves support with nothing to diagnose (defect, log it). Note this is invisible during normal use - it only appears once something has already gone wrong</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -16211,7 +16217,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89</t>
+          <t xml:space="preserve">88</t>
         </is>
       </c>
       <c r="C53" s="2"/>
@@ -16224,7 +16230,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="C54" s="2"/>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -269,13 +269,13 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_001, PA_006, PA_007, PA_012, PA_013
-PA_001/006/012/013 assert the URL only; PA_007 asserts the heading. No single test covers both.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-LOAD-01 (5 tests)
+Opens the page from the sidebar and asserts both the URL and the page &lt;h2&gt;, on IPG, BillPay, CommerceHub and SnapPay.</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -370,10 +370,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N3" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-LOAD-02
+Asserts the refresh icon is visible and that hovering it shows the tooltip text 'Refresh'.</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -396,7 +401,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: RefreshIcon present beside the heading on all four gateways.</t>
+          <t xml:space="preserve">QA 2026-09-16 BillPay and IPG: one RefreshIcon beside the heading, tooltip reads exactly 'Refresh' on hover.</t>
         </is>
       </c>
     </row>
@@ -466,13 +471,13 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_002, PA_008
-PA_002 checks a From Date control only (soft or-locator); PA_008 checks the Submit button. To Date is not covered.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-LOAD-03 (2 tests)
+Asserts From Date, To Date and Submit are all visible, that Submit is enabled, and that both pickers are pre-filled with a real MM/DD/YYYY hh:mm AM date.</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -570,10 +575,15 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N5" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-LOAD-04
+Reads both pickers, asserts To Date is today and that From Date is exactly 30 days earlier at 12:00 AM. From Date is derived from the To Date shown on screen, so a run straddling midnight cannot flake.</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -596,7 +606,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15: re-confirmed on a second day - defaults read 08/16/2026 to 09/15/2026, exactly 30 days, not the 1st of the previous month.</t>
+          <t xml:space="preserve">QA 2026-09-16 IPG and BillPay: page opened at 14:18 on 16 Sep showing From 08/17/2026 12:00 AM and To 09/16/2026 02:18 PM - a rolling 30-day window, confirming the module doc's 'first of the previous month' is wrong.</t>
         </is>
       </c>
     </row>
@@ -626,7 +636,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Network tab open</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -638,13 +648,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open DevTools &gt; Network and filter on 'payment_stats'
-2. Navigate to Payment Stats
-3. Verify a GET payment_stats_us request fires without any user action
-4. Verify fromDate and toDate match the pre-filled last-month window
-5. Verify flag=SUCCESS
-6. Verify the response returns HTTP 200
-7. Verify the table populates from that response</t>
+          <t xml:space="preserve">1. Navigate to Payment Stats from the sidebar
+2. Verify the refresh icon spins by itself, with no click from you - that is the page fetching on arrival
+3. Verify the spinning stops and the table fills with figures
+4. Verify From Date and To Date are pre-filled with the last-month window
+5. Verify you never pressed Submit at any point
+6. NOTE the refresh icon beside the 'Payment Stats' heading is the on-screen indicator that a request is in flight - it spins while the page is fetching and stops when the data lands. Watching it is enough; DevTools is not required for this case.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -669,10 +678,15 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N6" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-LOAD-05
+Arms the network wait before navigating, asserts the payment_stats_us call fires with no Submit click, returns 200, carries the window shown in the pickers, and that the table is populated by it.</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -695,7 +709,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: the call fires automatically on load with no Submit click - but it returns HTTP 400. See PS-NEG-11.</t>
+          <t xml:space="preserve">QA 2026-09-16 IPG, BillPay, CommerceHub, SnapPay, NuveiPaya, MerchantE: GET payment_stats_us fires on arrival with no Submit click, returns 200 and populates the table. IPG returned 8 payment-type rows.</t>
         </is>
       </c>
     </row>
@@ -742,7 +756,8 @@
 3. Verify flag=SUCCESS is present
 4. Change the date range and press Submit
 5. Verify the new request still sends flag=SUCCESS
-6. Verify no control anywhere on the page switches this to FAILED</t>
+6. Verify no control anywhere on the page switches this to FAILED - this half CAN be checked on screen
+7. NETWORK CHECK REQUIRED. This is one of only three Payment Analytics cases that cannot be judged from the screen - the value is never displayed, never configurable and leaves no visible trace, so DevTools is the only way to see it. Every other case in this module is checked on screen.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -767,10 +782,15 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N7" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-LOAD-06
+Captures the flag parameter of every payment_stats_us request across a page load and a Submit, and asserts every one of them is SUCCESS.</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -793,7 +813,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: flag=SUCCESS present on every request across all four gateways; no control offers FAILED.</t>
+          <t xml:space="preserve">QA 2026-09-16 IPG: every payment_stats_us request observed - on load and after Submit - carried flag=SUCCESS. Nothing on the page can send FAILED.</t>
         </is>
       </c>
     </row>
@@ -864,13 +884,18 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N8" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-LOAD-07 (3 tests)
+Measures the table and graph bounding boxes on IPG, CommerceHub and NuveiPaya and asserts the graph sits beside the table, with the table under 60% of the viewport width.</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -890,7 +915,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-16 measured at 1600px: IPG, CommerceHub and NuveiPaya all render table x155 w628 with the graph at x932 on the same row - side by side, table at 39% of the width.</t>
         </is>
       </c>
     </row>
@@ -960,13 +985,18 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N9" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-LOAD-08 (2 tests)
+Same measurement on BillPay and SnapPay, asserting the graph sits below a table wider than 80% of the viewport. Paymentus has no QA account.</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -986,7 +1016,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-16 measured at 1600px: BillPay and SnapPay render table x125 w1440 (90% of the width) with the graph below it at y698 - stacked, as specified. Paymentus has no QA account so that third gateway is untested.</t>
         </is>
       </c>
     </row>
@@ -1058,18 +1088,18 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_011
-Soft assertion - passes if a chart OR 'no rows' OR any row is visible, so an empty range and a broken page both pass.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-LOAD-09
+Submits a 2019 window that holds no payments, then asserts the headers survive, every payment-type row reads $0.00, the graph still renders, and no JavaScript error fires.</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1089,7 +1119,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-16 submitted 01/01/2019 to 01/02/2019. IPG returned 200 and rendered all eight payment-type rows reading $0.00 / 0 / 0. BillPay rendered the headers with a 'No rows' overlay. Neither produced a JavaScript error - the page degrades cleanly.</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1149,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; user with at least two sub-merchants; DevTools Network tab open</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; user with at least two sub-merchants</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1132,10 +1162,11 @@
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Payment Stats and note the figures in the table
-2. Switch to a different sub-merchant using the portal selector
-3. Verify a new payment_stats_us request is sent
-4. Verify it carries the new sub_merchant_id
-5. Verify the table and the graph both refresh with the new figures</t>
+2. Switch to a different sub-merchant using the portal selector at the top of the page
+3. Verify the refresh icon spins, showing the page is reloading for the new sub-merchant
+4. Verify the table figures change to the new sub-merchant's
+5. Verify the Payment Statistics graph redraws to match
+6. NOTE the refresh icon beside the 'Payment Stats' heading is the on-screen indicator that a request is in flight - it spins while the page is fetching and stops when the data lands. Watching it is enough; DevTools is not required for this case.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1160,13 +1191,18 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N11" s="2"/>
+          <t xml:space="preserve">Automated (expected fail)</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-LOAD-10
+Switches sub-merchant and asserts a new request goes out with the new sub_merchant_id and the figures change. Marked test.fail() because the product does neither - it will turn red the moment the defect is fixed.</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1186,7 +1222,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised - sub-merchant switching not driven in this run.</t>
+          <t xml:space="preserve">QA 2026-09-16 IPG, DEFECT CONFIRMED. The account has three sub-merchants (44052731, 44052728, 44052730). Switching from 44052731 to 44052728 changed the dropdown and the hidden input, but sent ZERO payment_stats_us requests and left the table showing the old figures unchanged. Editing a date and pressing Submit afterwards did fire a request - carrying the NEW sub_merchant_id and returning different figures - which proves the store was updated and only the refetch is missing.</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1271,7 @@
 4. Press Submit
 5. Verify the message 'Invalid date range' appears
 6. Verify the table data does not change
-7. Verify no stats request is sent</t>
+7. Verify the refresh icon does NOT spin - that is the on-screen proof nothing was sent</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1260,10 +1296,15 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N12" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-DATE-01
+Sets an inverted range with both dates in the past, then asserts the 'Invalid date range' toast appears, no request is sent and the table is untouched. Both dates stay in the past deliberately so the future-date branch, which returns earlier and silently, cannot fire instead.</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -1286,7 +1327,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 IPG: setting To Date earlier than From Date and pressing Submit produced the message 'Invalid date range' and fired zero stats requests.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG: set From 10 Sep, To 03 Sep (both past). Toast 'Invalid date range' appeared, zero payment_stats_us requests were sent and the table kept its previous figures. The toast auto-dismisses within a few seconds, so it must be asserted immediately, not read afterwards.</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1372,7 @@
           <t xml:space="preserve">1. Open Payment Stats
 2. Attempt to set From Date to a date after today
 3. Press Submit
-4. Verify no stats request is sent
+4. Verify the refresh icon does NOT spin, so nothing was sent
 5. Verify the table data does not change
 6. Verify NO error message, toast or inline hint is shown anywhere
 7. Record the silent rejection - the user gets no explanation why nothing happened</t>
@@ -1359,10 +1400,15 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N13" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-DATE-02
+Types a date a year ahead, confirms the field accepted it, then asserts NO request goes out, NO toast appears and the table is unchanged. The silence is asserted on purpose - it is the inconsistency this case exists to pin.</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -1385,7 +1431,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 IPG: setting From Date to a future date and pressing Submit fired zero stats requests and produced NO message of any kind - the silent rejection is confirmed, and it is inconsistent with the inverted-range case above.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG: the calendar cannot reach a future date, but typing 12/31/2027 into From Date IS accepted by the field. Pressing Submit then produced NO request, NO toast and no change on screen. The rejection is completely silent, unlike the inverted-range case - confirmed in source at controller.js:32-38, where the future branch returns before the toast line.</t>
         </is>
       </c>
     </row>
@@ -1430,13 +1476,14 @@
 2. Open the From Date picker calendar
 3. Navigate to the current month
 4. Verify dates after today are greyed out and cannot be clicked
-5. Navigate to a future month and verify every date is unselectable
-6. Repeat for the To Date picker</t>
+5. Verify today itself IS selectable - it is the last enabled day
+6. Verify the forward (next month) arrow is DISABLED, so a future month cannot be reached at all
+7. Repeat for the To Date picker</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Both calendars disable every date after today, so future dates cannot be picked through the UI at all</t>
+          <t xml:space="preserve">Both calendars disable every date after today, and the next-month arrow is disabled on the current month, so a future month cannot even be opened. This is stricter than simply greying out future days</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1456,13 +1503,18 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N14" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-DATE-03
+On both pickers: asserts today is the last selectable day, every disabled day is after today, and the next-month arrow is disabled so a future month cannot be reached at all.</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified</t>
+          <t xml:space="preserve">Corrected after run</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1482,7 +1534,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 IPG: opening the From calendar and stepping to the current month showed 18 disabled days against 17 enabled - future dates are blocked. Navigation past the current month was also refused.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG, case reworded. Future days ARE greyed out in the current month - on 17 Sep, days 18-30 were disabled and 17 was the last enabled day. But the original step 5 could not be performed: the next-month arrow is DISABLED once the current month is displayed, so a future month cannot be opened at all. The product is stricter than the case assumed.</t>
         </is>
       </c>
     </row>
@@ -1553,10 +1605,15 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N15" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-DATE-04
+Sets From Date to the 15th of last month and asserts the To calendar disables the 1st to the 14th; then moves From Date to the 20th and asserts the floor follows to the 19th.</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -1579,7 +1636,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 IPG: the To calendar opened on the current month; stepping back to the From month showed 21 disabled days against 21 enabled - dates before the selected From Date are blocked.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG: with From Date on 15 Aug, the To Date calendar for August disabled 1-14 and enabled 15 onwards. Moving From Date to 20 Aug moved the floor - 1-19 disabled, 20 enabled. Note the calendar keeps BOTH months mounted for about 500ms while it slides, so day cells must be read after the transition settles or two months are counted at once.</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1666,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Network tab open</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1624,9 +1681,10 @@
           <t xml:space="preserve">1. Open Payment Stats and note the figures in the table
 2. Change From Date to three months earlier
 3. Press Submit
-4. Verify a payment_stats_us request is sent with the new fromDate
+4. Verify the refresh icon spins, showing the wider range was sent
 5. Verify the table figures update
-6. Verify the statistics graph percentages update to match</t>
+6. Verify the statistics graph percentages update to match
+7. NOTE the refresh icon beside the 'Payment Stats' heading is the on-screen indicator that a request is in flight - it spins while the page is fetching and stops when the data lands. Watching it is enough; DevTools is not required for this case.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1651,13 +1709,13 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_E2E_DATE_SUBMIT
-Drives a date change then Submit, but the date entry is wrapped in an if-visible guard and the final assertion is a three-way or - it passes whether or not Submit did anything.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-DATE-05
+Widens From Date to three months back, confirms the picker accepted it, then asserts Submit re-queries payment_stats_us with a 200 and the grid repopulates.</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1712,7 +1770,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Network tab open</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1726,9 +1784,10 @@
           <t xml:space="preserve">1. Open Payment Stats and note the figures
 2. Change To Date to an earlier date still after From Date
 3. Press Submit
-4. Verify the request carries the new toDate
+4. Verify the refresh icon spins and the To Date on screen is the new one
 5. Verify the totals drop or stay the same, never increase
-6. Verify the graph updates to match</t>
+6. Verify the graph updates to match
+7. NOTE the refresh icon beside the 'Payment Stats' heading is the on-screen indicator that a request is in flight - it spins while the page is fetching and stops when the data lands. Watching it is enough; DevTools is not required for this case.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1753,13 +1812,18 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N17" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-DATE-06
+Loads a 60-day window, pulls the To Date back to 30 days, and asserts the request carries the new toDate and the total quantity never grows when the window shrinks.</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1779,7 +1843,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG: a 60-day window then the same window cut back to 30 days. The second request carried the new toDate and the total quantity did not grow.</t>
         </is>
       </c>
     </row>
@@ -1851,13 +1915,18 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N18" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-DATE-07
+Submits a start-of-day to end-of-day range, asserts no validation toast, that both ends of the request are that same day, and that the table renders. The Transactions cross-check in step 6 stays manual by agreement.</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -1877,7 +1946,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG: start-of-day to end-of-day on a single day is accepted with no validation message, and both ends of the request carry that same date. Single-day figures observed on several days - 15 Sep returned 47 card payments, 12 Sep returned none. The Transactions cross-check in step 6 has not been automated and remains a manual step.</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1991,7 @@
 2. Clear the From Date field completely
 3. Verify the page does not crash and the table keeps its previous data
 4. Press Submit
-5. Verify no stats request is sent with an empty date
+5. Verify the refresh icon does NOT spin, so no request went out with an empty date
 6. Re-enter a valid From Date and verify Submit works again</t>
         </is>
       </c>
@@ -1948,10 +2017,15 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N19" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-DATE-08
+Clears From Date, asserts the field falls back to its format placeholder, the table keeps its data, Submit sends nothing, and a valid date restores normal behaviour.</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -1974,7 +2048,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 IPG: clearing the From field left the placeholder showing and pressing Submit fired ZERO stats requests, so no blank range reaches the API.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG: Ctrl+A then Delete empties From Date, which falls back to showing 'MM/DD/YYYY hh:mm aa'. The table kept its data, Submit sent no request at all, and entering a valid date restored normal behaviour. Note Submit is NOT disabled while the field is empty - that is PS-SUB-02.</t>
         </is>
       </c>
     </row>
@@ -2018,14 +2092,14 @@
           <t xml:space="preserve">1. Open Payment Stats
 2. Type '13/45/2026' into the From Date field
 3. Verify the value is not accepted as a valid date
-4. Verify the page does not crash and no request is sent
+4. Verify the page does not crash and the refresh icon does not spin, so nothing was sent
 5. Repeat with a text string such as 'abcd'
 6. Clear the field and enter a valid date to confirm recovery</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invalid date text is rejected outright; the page keeps working and no malformed range reaches the API</t>
+          <t xml:space="preserve">No malformed date ever reaches the API and the page keeps working. NOTE the input is NOT rejected - the picker silently REWRITES it to a different valid date (13/45/2026 becomes 03/04/2026; abcd leaves the previous value). A merchant can therefore query a date they never typed, with no indication anything was changed. Logged as a usability defect</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2045,10 +2119,15 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N20" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-DATE-09
+Types 13/45/2026, abcd and 00/00/0000 and asserts the field always holds a well-formed date and nothing malformed reaches the API. Asserts the real behaviour, not the original wording - the picker rewrites bad input rather than rejecting it, which is logged separately as a defect.</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Corrected after run</t>
@@ -2071,7 +2150,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 IPG: CORRECTED - typing '13/45/2026 99:99 XX' is not rejected. The picker coerces it to a valid date (observed '03/04/2026 09:09 AM') and Submit then fires a normal request. The original expectation of 'no request is sent' was wrong; the page stays stable, which is the real point.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG, expected result rewritten. The input is NOT rejected. The picker silently rewrites it: '13/45/2026' left 03/04/2026 in the field, 'abcd' left the previous date untouched, '00/00/0000' left the previous date. The field never holds malformed text and nothing malformed reaches the API, so the safety property holds - but a merchant can query a date they never typed with no indication anything changed. Raised as a usability defect.</t>
         </is>
       </c>
     </row>
@@ -2143,13 +2222,18 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N21" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-DATE-10
+Walks back up to 14 days to find one with payments both before and after midday, then asserts the half-day window returns fewer than the full day. Discovers its own date so it cannot go stale; if no suitable day exists it fails naming every day it examined.</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2169,7 +2253,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG: the time of day is honoured, not just the date. On 15 Sep, 00:00 to 12:00 returned 6 payments totalling $60.00 while 00:00 to 23:59 returned 47 totalling $1,984.00. The automated test discovers a suitable day at runtime rather than hard-coding one, so it does not go stale as QA data ages.</t>
         </is>
       </c>
     </row>
@@ -2247,13 +2331,18 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N22" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-DATE-11
+Walks 1 day, 1 week, 1 month, 2 months and 3 months, all ending now. Asserts each range loads with no toast, that totals never shrink as the window widens, and that the graph agrees with the table for every range - a bar for each payment type with activity, none for those without, and each bar's caption and width equal to that row's Qty(%).</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2271,7 +2360,11 @@
           <t xml:space="preserve">PaymentAnalytics/index.js:185-202</t>
         </is>
       </c>
-      <c r="S22" s="2"/>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QA 2026-09-17 IPG: 1 day, 1 week, 1 month, 2 months and 3 months all loaded with no error and no validation message, and the totals never shrank as the window widened. The graph agreed with the table at every range - statsGraph/index.jsx only renders a row when qtyPerc &gt; 0, so a payment type with zero quantity has no bar at all, and each bar's caption and inline width equal that row's Qty(%).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2">
@@ -2299,35 +2392,35 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Network tab open; page freshly loaded and untouched</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; page freshly loaded and untouched - do not click anything before starting</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Action: press Submit without editing either date
-Expected: no request at all
+          <t xml:space="preserve">Action: press Submit ONCE on a freshly loaded page, then press it a second time
+Expected: the first press is ignored, the second works
 Gateway: any - behaviour is identical on every gateway</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Payment Stats and let the initial data load
-2. Open DevTools &gt; Network and clear the log
-3. Without touching either date field, press Submit
-4. Watch the network log for 10 seconds
-5. Verify NO payment_stats_us request is sent
-6. Verify nothing on the page changes - no spinner, no refresh, no message
-7. Now change a date, press Submit, and verify a request does fire</t>
+          <t xml:space="preserve">1. Open Payment Stats from the sidebar and let the initial data load fully
+2. Without touching either date field, press Submit ONCE
+3. Watch the refresh icon beside the heading for 10 seconds
+4. Verify it does NOT spin and nothing on the page changes - the click was swallowed
+5. Now press Submit a SECOND time, still without touching any date
+6. Verify the icon DOES spin this time and the page reloads
+7. NOTE the refresh icon beside the 'Payment Stats' heading is the on-screen indicator that a request is in flight - it spins while the page is fetching and stops when the data lands. Watching it is enough; DevTools is not required for this case.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit is inert until a date is edited. Pressing it on a freshly loaded page silently does nothing, which reads as a broken button to the user (defect, log it)</t>
+          <t xml:space="preserve">Submit re-runs the query for the window on screen every time it is pressed, whether or not a date was edited. CURRENTLY DEFECTIVE: on a freshly loaded page it does nothing at all - no request, no spinner, no message - so the button simply reads as broken. The automated test asserts the correct behaviour and is marked as an expected failure until this is fixed</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2342,18 +2435,18 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated (expected fail)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_E2E_DATE_SUBMIT
-The only test that clicks Submit. It cannot detect the inert-Submit defect because its assertion passes on a chart being present.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-01
+Its own test now. Lets the page settle, confirms neither date was edited, then asserts Submit starts a fetch. Marked test.fail() because it does not. Manual step 7 - change a date and confirm a request fires - is covered for real by PS-DATE-05.</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified</t>
+          <t xml:space="preserve">Corrected after run</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2373,7 +2466,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: CONFIRMED on IPG, SnapPay and CommerceHub - pressing Submit without editing a date sent ZERO requests each time. The button is genuinely inert on a freshly loaded page.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG, DEFECT CONFIRMED but narrower than first written - corrected after a second round of measurement. It is the FIRST click after page load that is swallowed, not Submit in general. Measured on a freshly loaded page: click 1 produced no request and no spinner, click 2 spun and returned HTTP 200, click 3 the same. An earlier note said Submit stays inert 'until a date is edited' - that is wrong. No date edit is needed; the first click is itself what clears the flag, so any second interaction works. Isdateset starts true and the handler checks !Isdateset on the line after calling setDateSet(false), before React has applied it.</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2518,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit is never visually disabled regardless of the date state, so the user gets no advance warning that a range is invalid (defect, log it)</t>
+          <t xml:space="preserve">Submit is greyed out while the date range cannot be used, so the merchant is warned before clicking rather than after. CURRENTLY DEFECTIVE: the button is never disabled in any state. The component builds and maintains an isSubmitButtonDisabled state throughout, but the line that consumes it is commented out at PaymentAnalytics/index.js:606 - // disabled={isSubmitButtonDisabled}. The automated test asserts the intended behaviour and is marked as an expected failure until that line is restored</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2445,13 +2538,18 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N24" s="2"/>
+          <t xml:space="preserve">Automated (expected fail)</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-02
+Clears From Date and asserts Submit is disabled, then inverts the range and asserts the same. Marked test.fail(): the button is never disabled because index.js:606 has the disabled prop commented out.</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified</t>
+          <t xml:space="preserve">Corrected after run</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -2471,7 +2569,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: the Submit button rendered enabled on every gateway regardless of date state.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG, DEFECT CONFIRMED with source evidence, expected result rewritten. Submit reported enabled in every state tested: on load, with the range inverted, and with From Date cleared entirely - the disabled attribute was absent throughout. The cause is not missing logic: isSubmitButtonDisabled is declared at index.js:86 and updated in five places, but the line that applies it is commented out at index.js:606 - // disabled={isSubmitButtonDisabled}. Uncommenting it is the whole fix.</t>
         </is>
       </c>
     </row>
@@ -2517,9 +2615,9 @@
 2. Change From Date to six months back and press Submit
 3. Confirm the table reflects the wider range
 4. Click the refresh icon
-5. Verify From Date returns to the 1st of last month at 00:00:00
+5. Verify From Date returns to exactly 30 days before today at 12:00 AM - NOT the 1st of last month, the same wording error corrected in PS-LOAD-04
 6. Verify To Date returns to today at the current time
-7. Verify the table reloads for that default window</t>
+7. Verify the refresh icon spins, and the table reloads for that default window</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2544,13 +2642,18 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N25" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-03
+Widens the window to six months and submits, then clicks refresh and asserts both dates return to the default 30-day window, the icon spins, and the table reloads with no more payments than the wider window held.</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Corrected after run</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -2570,7 +2673,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG, works as intended; step 5 wording corrected. Widened From Date to six months back and submitted, then clicked refresh: From Date returned to 08/18/2026 12:00 AM and To Date to today, the refresh icon spun, a fresh request went out and the table reloaded with the narrower figures. Note the written step said From Date returns to 'the 1st of last month' - it does not. getLastMonth() is a rolling 30-day window, the same error already corrected in PS-LOAD-04.</t>
         </is>
       </c>
     </row>
@@ -2600,22 +2703,24 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Network tab open</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; page freshly loaded - do not click anything before starting</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Action: click the refresh icon and watch the animation
+          <t xml:space="preserve">Action: click the refresh icon twice and watch the animation
 Gateway: any - behaviour is identical on every gateway</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Payment Stats
-2. Click the refresh icon
-3. Verify the icon animates while the request is running
-4. Verify a payment_stats_us request is sent
-5. Verify the animation stops once the response arrives</t>
+          <t xml:space="preserve">1. Open Payment Stats from the sidebar and let the data load fully
+2. Click the refresh icon ONCE
+3. Verify it does NOT animate - the first click after page load is swallowed (see PS-SUB-01, same cause)
+4. Click the refresh icon a SECOND time
+5. Verify it now animates while the data reloads
+6. Verify the animation stops once the figures come back
+7. NOTE the refresh icon beside the 'Payment Stats' heading is the on-screen indicator that a request is in flight - it spins while the page is fetching and stops when the data lands. Watching it is enough; DevTools is not required for this case.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2640,13 +2745,18 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N26" s="2"/>
+          <t xml:space="preserve">Automated (expected fail)</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-04
+Lets the page settle, clicks refresh and asserts the icon starts spinning. Marked test.fail(): on a freshly loaded page refresh does nothing at all.</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified</t>
+          <t xml:space="preserve">Corrected after run</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -2666,7 +2776,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 BillPay: the refresh icon's class changed on click, confirming the animation is applied. The exact spin class was not captured because it clears after about a second.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG, DEFECT CONFIRMED, wording corrected after re-measurement. The refresh icon is not dead - it ignores exactly one click, the first after page load. Sampling the icon class every 40ms: click 1 never span and sent no request, click 2 span and returned HTTP 200, click 3 the same. An earlier note said it 'only works once a Submit has run' - that is wrong, a second refresh click is enough on its own. Same !Isdateset gate as PS-SUB-01, and one fix clears both.</t>
         </is>
       </c>
     </row>
@@ -2738,10 +2848,15 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N27" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-05
+Expands Prepare Query on BillPay, confirms Select, Group and Having plus Execute and Cancel, then asserts refresh collapses the panel and leaves the default columns intact.</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -2764,7 +2879,7 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 BillPay: clicking the refresh icon collapsed the expanded Prepare Query panel.</t>
+          <t xml:space="preserve">QA 2026-09-17 BillPay: expanded Prepare Query and confirmed the Select, Group and Having controls plus Execute and Cancel. Clicking refresh collapsed the whole panel - Execute and Cancel both gone - and the table kept its six default columns. The panel collapse is NOT affected by the Isdateset gate, because the handler resets the columns and closes the filter before reaching the fetch.</t>
         </is>
       </c>
     </row>
@@ -2835,13 +2950,18 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N28" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-06
+Trims the Select list to two fields and executes, asserts the table narrows to those plus Amount and Count and that a dropped column really left, then asserts refresh restores the full default set.</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -2861,7 +2981,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-17 BillPay: trimmed the Select list from four fields to two (Funding Method, Funding Category) and clicked Execute. The table rebuilt with exactly Category, Funding Method, Amount and Count - Channel and Displayed Fee Amount were gone. Clicking refresh restored all six default columns and closed the panel.</t>
         </is>
       </c>
     </row>
@@ -2891,7 +3011,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Network tab open</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2902,12 +3022,13 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Payment Stats and open DevTools &gt; Network
-2. Change the From Date
-3. Click Submit three times in quick succession
-4. Count the payment_stats_us requests sent
-5. Verify the table ends up consistent with the selected range
-6. Record the request count if more than one fires per click</t>
+          <t xml:space="preserve">1. Open Payment Stats and set a narrow date range, press Submit once and write down the figures
+2. Widen the range considerably, press Submit, and confirm the figures change
+3. Set the narrow range back again
+4. Click Submit three times in quick succession
+5. Wait for the refresh icon to stop spinning
+6. Verify the figures match what step 1 recorded, NOT the wider range - a mismatch means a stale response overwrote a newer one
+7. NOTE the refresh icon beside the 'Payment Stats' heading is the on-screen indicator that a request is in flight - it spins while the page is fetching and stops when the data lands. Watching it is enough; DevTools is not required for this case.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2932,10 +3053,15 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N29" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-07
+Records the figures for a calm single submit, switches to a much wider window, then returns and clicks Submit three times in a burst. Asserts the resulting table matches the calm result exactly, so no stale response won.</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -2958,7 +3084,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 SnapPay: three rapid Submit clicks produced three stats requests - there is no debouncing. The table stayed consistent with the selected range. Watch for a slow earlier response overwriting a newer one on a loaded environment.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG: submitted a 3-day window and recorded its figures, widened to 90 days, then returned to the 3-day window and clicked Submit three times in quick succession. The dates on screen and every figure in the table matched the calm single-submit result exactly - no stale response overwrote a newer one.</t>
         </is>
       </c>
     </row>
@@ -3001,10 +3127,11 @@
         <is>
           <t xml:space="preserve">1. Open DevTools &gt; Network and open Payment Stats
 2. Inspect the payment_stats_us query string
-3. Note the clientRequestId value
+3. Note the clientRequestId value - observed as 1647602068707
 4. Change a date and press Submit
 5. Inspect the new request and compare the clientRequestId
-6. Verify it is the same fixed value on both calls rather than a per-request identifier</t>
+6. Verify it is the same fixed value on both calls rather than a per-request identifier
+7. NETWORK CHECK REQUIRED. This is one of only three Payment Analytics cases that cannot be judged from the screen - the value is never displayed, never configurable and leaves no visible trace, so DevTools is the only way to see it. Every other case in this module is checked on screen.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3029,10 +3156,15 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N30" s="2"/>
+          <t xml:space="preserve">Automated (expected fail)</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-08
+Collects clientRequestId from two separate calls and asserts they differ. Marked test.fail(): the value is hard-coded. One of only three network reads in the module - the parameter has no UI surface.</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -3055,7 +3187,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: clientRequestId=1647602068707 was identical on every request across all four gateways.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG, DEFECT CONFIRMED. Every payment_stats_us call carried clientRequestId=1647602068707, the same fixed value on page load and after a date change, exactly as apis/payment.js:101 hard-codes it. Two requests cannot be told apart in logs or traced individually. This is one of only three places in the module where the test reads the network, because the parameter has no UI surface of any kind.</t>
         </is>
       </c>
     </row>
@@ -3130,13 +3262,13 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_010, PA_012
-PA_010 is a soft or-assertion (Type OR Amount OR Qty), so it cannot detect a missing column; PA_012 only asserts the URL after logging in as CommerceHub.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-COL-01 (3 tests)
+Asserts all five payment-type columns are present on IPG, CommerceHub and NuveiPaya, and that no BillPay-only column leaks in. Column order is deliberately not asserted.</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3234,13 +3366,13 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_003, PA_009
-PA_003 only asserts the header count is above zero; PA_009 hard-asserts 3 of the 6 BillPay columns (Funding Method, Amount, Count).</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-COL-03 (2 tests)
+Asserts all six BillPay columns are present and that a standard-gateway column does not leak in.</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -7270,13 +7402,13 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_004, PA_014, PA_018, PA_019, PA_020 | payment-trends.spec.ts :: 'View Payment Trends page', 'Payment Trends with WGL user'
-PA_004 asserts the URL; PA_014 asserts the heading text; the rest assert a heading or 'no data' per gateway.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-LOAD-01 (3 tests)
+Opens Payment Trends from the sidebar and asserts the URL, the page &lt;h2&gt; and the 'Payments Month' caption, on BillPay and IPG.</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -7369,10 +7501,15 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N74" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-LOAD-02
+Asserts the grey sub-heading reads exactly 'Payment Trends in &lt;current year&gt;'.</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -7465,10 +7602,15 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N75" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-LOAD-03
+Asserts the refresh icon is visible and shows the tooltip 'Refresh' on hover.</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -7559,13 +7701,13 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_015
-Soft assertion - passes if any 'Last N Months' text OR any select/combobox is visible. Does not check that the default is Last 6 Months.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-LOAD-04
+Asserts the range control reads Last 6 Months on load and that opening it offers exactly the four expected options in order.</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -7661,13 +7803,13 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_005, PA_016 | payment-trends.spec.ts :: 'Payment Trends shows chart'
-All three are soft; the payment-trends.spec.ts one only console.logs the result and asserts nothing at all.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-LOAD-05
+Asserts both axis captions are drawn and that the chart carries at least one month label.</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -7765,13 +7907,13 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_016
-Soft assertion - passes if a chart element OR any 'payments' text is visible. Month labels are never counted or read.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-LOAD-06
+Counts exactly six month labels and asserts the newest one is the current month and year.</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -7871,10 +8013,15 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N79" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-LOAD-07
+Asserts the periodic_payment_stats_us call on load returns 200 and carries pageDefination=monthly, pageNumber=1, pageSize=6 and a non-empty sub_merchant_id.</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Corrected after run</t>
@@ -7968,10 +8115,15 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N80" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-LOAD-08
+Asserts the selected-month heading, export links, summary cards and transaction table are all absent until a bar is clicked.</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -8066,10 +8218,15 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N81" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-LOAD-09
+Loads Trends for a merchant with no payments and asserts the chart still draws six labelled months with no JavaScript error. Currently FAILS - see the defect table.</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -8163,10 +8320,15 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N82" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-LOAD-10
+Counts the SVGs that contain numeric tick labels and asserts exactly one value axis paints. Encodes a known defect - invert it if the right-hand axis is ever wired up.</t>
+        </is>
+      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Corrected after run</t>
@@ -8356,13 +8518,13 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_015, PA_E2E_TRENDS_RANGE
-Neither enumerates the four options; PA_E2E_TRENDS_RANGE only asserts a chart container is visible.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-RANGE-01
+Enumerates the four range options and asserts their labels and count.</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -8460,13 +8622,13 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_E2E_TRENDS_RANGE
-Changes the range but asserts only that a chart is still visible - no label count, no pageSize check.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-RANGE-02
+Selects Last 3 Months, asserts the API is re-queried with pageSize=3 and that the chart redraws with exactly three labels.</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -8564,13 +8726,13 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_E2E_TRENDS_RANGE
-Same test; rotation and label count are not checked.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-RANGE-03
+Same for Last 12 and Last 24 Months, and additionally asserts the labels are rotated once the range exceeds six months.</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -9060,13 +9222,13 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_017
-Soft assertion - passes if ACH OR Card text is visible, and is run on one gateway only. Cannot detect a wrong legend on any of the three.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-LEG-01
+Asserts the BillPay legend reads exactly ['Ach', 'Card'].</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -9165,13 +9327,13 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: PA_019, PA_020
-Both only assert a heading or 'no data' after logging in as CommerceHub / SnapPay - neither checks the legend, and MerchantE is not covered at all.</t>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PT-LEG-04 (2 tests)
+Asserts the CommerceHub and SnapPay legends settle on exactly ['Token', 'Card']. Polls, because the legend first paints from the default gateway and repaints once the periodic response resolves.</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -15723,7 +15885,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -15735,276 +15897,292 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial</t>
+          <t xml:space="preserve">Automated (expected fail)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">An existing test touches the area but asserts too weakly to catch a regression</t>
+          <t xml:space="preserve">A spec test covers the case and asserts the CORRECT behaviour, but the product is defective, so the test is marked test.fail(). It turns red when the defect is fixed</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Partial</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No spec test goes near this case</t>
+          <t xml:space="preserve">An existing test touches the area but asserts too weakly to catch a regression</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Not Automated</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No spec test goes near this case</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suite run</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 passed, 1 failed</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the failure is a broken locator in PA_E2E_DATE_SUBMIT, not a product bug. The 24 passes happened while Payment Stats was returning 400 on every request</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43 passed, 0 failed (2026-09-16)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the whole tests/customer/payment-analytics/ folder on QA, chromium. PS-LOAD-10 counts as a pass because it is marked test.fail() - it asserts the correct behaviour against an open defect</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verification run</t>
-        </is>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automation note</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Token injection alone does not load Payment Stats</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">injectCustomerAuthByType writes the token into an already-mounted app; App.js only reads it on mount to fetch the country code, and Payment Stats refuses to fetch while that is empty. Every Stats test now calls reloadAfterAuthInjection() first. Payment Trends never needed it</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Environment</t>
+          <t xml:space="preserve">Verification method</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA</t>
-        </is>
-      </c>
-      <c r="C21" s="2"/>
+          <t xml:space="preserve">On screen, not in DevTools</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the manual steps were rewritten to judge everything from the page itself. The refresh icon beside the heading spins while a request is in flight and stays still when none was sent, so it answers both "did it fetch?" and "did it correctly NOT fetch?" without opening DevTools. The automated tests use the same signal</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accounts exercised</t>
+          <t xml:space="preserve">Cases that still need DevTools</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">one account per gateway: IPG, BillPay, MerchantE, CommerceHub, SnapPay, NuveiPaya</t>
-        </is>
-      </c>
-      <c r="C22" s="2"/>
+          <t xml:space="preserve">3 of 155</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PS-LOAD-06 (flag=SUCCESS), PS-SUB-08 (clientRequestId) and PT-LOAD-07 (pageNumber). Each is a query parameter that is never displayed, never configurable and leaves no visible trace, so the screen genuinely cannot answer the question. Every other case is checked on screen</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gateways with no QA account</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paymentus, India</t>
-        </is>
-      </c>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
       <c r="C23" s="2"/>
     </row>
     <row r="24">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verification run</t>
+        </is>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verification outcome</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cases</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meaning</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Environment</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QA</t>
+        </is>
+      </c>
+      <c r="C25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified</t>
+          <t xml:space="preserve">Accounts exercised</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed directly on QA - includes cases that FAILED and produced a defect</t>
-        </is>
-      </c>
+          <t xml:space="preserve">one account per gateway: IPG, BillPay, MerchantE, CommerceHub, SnapPay, NuveiPaya</t>
+        </is>
+      </c>
+      <c r="C26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gateways with no QA account</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paymentus, India</t>
+        </is>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verification outcome</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cases</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verified</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed directly on QA - includes cases that FAILED and produced a defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Corrected after run</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Case was wrong against the real app and has been rewritten</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Blocked</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Merchant has no usable data on QA</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not verified</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not exercised - Stats cases blocked behind the 400; E2E cases need approval to create payments on QA</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Section</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cases</t>
-        </is>
-      </c>
-      <c r="C31" s="1"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1. End-to-End Payment Flows</t>
+          <t xml:space="preserve">Blocked</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
-      <c r="C32" s="2"/>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merchant has no usable data on QA</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S1. Page Load &amp; Layout</t>
+          <t xml:space="preserve">Not verified</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
-      <c r="C33" s="2"/>
+          <t xml:space="preserve">48</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not exercised - Stats cases blocked behind the 400; E2E cases need approval to create payments on QA</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S2. Date Range &amp; Validation</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
       <c r="C34" s="2"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S3. Submit &amp; Refresh</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="C35" s="2"/>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Section</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cases</t>
+        </is>
+      </c>
+      <c r="C35" s="1"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S4. Gateway Table Columns</t>
+          <t xml:space="preserve">E1. End-to-End Payment Flows</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="C36" s="2"/>
@@ -16012,12 +16190,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S5. Prepare Query</t>
+          <t xml:space="preserve">S1. Page Load &amp; Layout</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="C37" s="2"/>
@@ -16025,12 +16203,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S6. Statistics Graph</t>
+          <t xml:space="preserve">S2. Date Range &amp; Validation</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="C38" s="2"/>
@@ -16038,12 +16216,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S7. Negative &amp; Data Integrity</t>
+          <t xml:space="preserve">S3. Submit &amp; Refresh</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="C39" s="2"/>
@@ -16051,12 +16229,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T1. Page Load &amp; Layout</t>
+          <t xml:space="preserve">S4. Gateway Table Columns</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="C40" s="2"/>
@@ -16064,12 +16242,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T2. Time Range Selection</t>
+          <t xml:space="preserve">S5. Prepare Query</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="C41" s="2"/>
@@ -16077,12 +16255,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T3. Chart Legend &amp; Series</t>
+          <t xml:space="preserve">S6. Statistics Graph</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="C42" s="2"/>
@@ -16090,12 +16268,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T4. Chart Tooltip</t>
+          <t xml:space="preserve">S7. Negative &amp; Data Integrity</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="C43" s="2"/>
@@ -16103,7 +16281,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T5. Month Drill-Down</t>
+          <t xml:space="preserve">T1. Page Load &amp; Layout</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -16116,12 +16294,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T6. Summary Cards</t>
+          <t xml:space="preserve">T2. Time Range Selection</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="C45" s="2"/>
@@ -16129,12 +16307,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T7. Transaction Table &amp; Pagination</t>
+          <t xml:space="preserve">T3. Chart Legend &amp; Series</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="C46" s="2"/>
@@ -16142,7 +16320,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T8. Export</t>
+          <t xml:space="preserve">T4. Chart Tooltip</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -16155,12 +16333,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T9. Refresh</t>
+          <t xml:space="preserve">T5. Month Drill-Down</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="C48" s="2"/>
@@ -16168,43 +16346,51 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T10. Negative &amp; Data Integrity</t>
+          <t xml:space="preserve">T6. Summary Cards</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="C49" s="2"/>
     </row>
     <row r="50">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T7. Transaction Table &amp; Pagination</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
       <c r="C50" s="2"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Priority</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cases</t>
-        </is>
-      </c>
-      <c r="C51" s="1"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T8. Export</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical</t>
+          <t xml:space="preserve">T9. Refresh</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="C52" s="2"/>
@@ -16212,56 +16398,56 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">T10. Negative &amp; Data Integrity</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="C53" s="2"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43</t>
-        </is>
-      </c>
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
       <c r="C54" s="2"/>
     </row>
     <row r="55">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priority</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cases</t>
+        </is>
+      </c>
+      <c r="C55" s="1"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gateway</t>
-        </is>
-      </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cases</t>
-        </is>
-      </c>
-      <c r="C56" s="1"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="C56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">all gateways</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">88</t>
         </is>
       </c>
       <c r="C57" s="2"/>
@@ -16269,51 +16455,43 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BillPay</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="C58" s="2"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IPG</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
       <c r="C59" s="2"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SnapPay</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="C60" s="2"/>
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gateway</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cases</t>
+        </is>
+      </c>
+      <c r="C60" s="1"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">India</t>
+          <t xml:space="preserve">all gateways</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="C61" s="2"/>
@@ -16321,12 +16499,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MerchantE</t>
+          <t xml:space="preserve">BillPay</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="C62" s="2"/>
@@ -16334,12 +16512,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paymentus</t>
+          <t xml:space="preserve">IPG</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="C63" s="2"/>
@@ -16347,12 +16525,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BillPay, SnapPay, MerchantE, NuveiPay</t>
+          <t xml:space="preserve">SnapPay</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="C64" s="2"/>
@@ -16360,12 +16538,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MerchantE, SnapPay, CommerceHub</t>
+          <t xml:space="preserve">India</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="C65" s="2"/>
@@ -16373,12 +16551,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IPG, CommerceHub, NuveiPaya</t>
+          <t xml:space="preserve">MerchantE</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="C66" s="2"/>
@@ -16386,12 +16564,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IPG, BillPay, NuveiPaya</t>
+          <t xml:space="preserve">Paymentus</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="C67" s="2"/>
@@ -16399,273 +16577,393 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CommerceHub</t>
+          <t xml:space="preserve">BillPay, SnapPay, MerchantE, NuveiPay</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C68" s="2"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MerchantE, SnapPay, CommerceHub</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C69" s="2"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IPG, CommerceHub, NuveiPaya</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="C68" s="2"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defects confirmed on QA</t>
-        </is>
-      </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Test Case</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What was observed</t>
-        </is>
-      </c>
+      <c r="C70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Payment Stats loses its data on refresh</t>
+          <t xml:space="preserve">IPG, BillPay, NuveiPaya</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-NEG-11</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reached from the sidebar it works; a refresh or direct URL sends an empty sub_merchant_id and returns 400</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stats page fails silently</t>
+          <t xml:space="preserve">CommerceHub</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-NEG-01</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the refresh 400 produces no toast, no banner, no message - it looks like a merchant with no payments</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C72" s="2"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Submit does nothing until a date is edited</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PS-SUB-01</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zero requests sent on three gateways tested</t>
-        </is>
-      </c>
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Submit is never disabled</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PS-SUB-02</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">button enabled regardless of date state</t>
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defects confirmed on QA</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test Case</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What was observed</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Default range is 30 days, not last month</t>
+          <t xml:space="preserve">Payment Stats loses its data on refresh</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-LOAD-04</t>
+          <t xml:space="preserve">PS-NEG-11</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">observed a 30-day window; the module doc is wrong</t>
+          <t xml:space="preserve">reached from the sidebar it works; a refresh or direct URL sends an empty sub_merchant_id and returns 400</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Default range may break in Oct-Dec</t>
+          <t xml:space="preserve">Stats page fails silently</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-NEG-12</t>
+          <t xml:space="preserve">PS-NEG-01</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">month behind a fixed leading zero - run in October</t>
+          <t xml:space="preserve">the refresh 400 produces no toast, no banner, no message - it looks like a merchant with no payments</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chart and drill-down disagree</t>
+          <t xml:space="preserve">Default range is 30 days, not last month</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT-NEG-12</t>
+          <t xml:space="preserve">PS-LOAD-04</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tooltip reported hundreds of card payments, drill-down returned 0 rows</t>
+          <t xml:space="preserve">observed a 30-day window; the module doc is wrong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card count 0 beside a real amount</t>
+          <t xml:space="preserve">Default range may break in Oct-Dec</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT-NEG-13</t>
+          <t xml:space="preserve">PS-NEG-12</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">summary card read "Card (0)" with a non-zero amount</t>
+          <t xml:space="preserve">month behind a fixed leading zero - run in October</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trends periodic stats returns 400</t>
+          <t xml:space="preserve">Chart and drill-down disagree</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT-NEG-01</t>
+          <t xml:space="preserve">PT-NEG-12</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 400 "Merchant not exists", no message shown</t>
+          <t xml:space="preserve">tooltip reported hundreds of card payments, drill-down returned 0 rows</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gateway falls back to ACH layout</t>
+          <t xml:space="preserve">Card count 0 beside a real amount</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT-NEG-11</t>
+          <t xml:space="preserve">PT-NEG-13</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">portal header showed the real gateway but the legend rendered Ach+Card</t>
+          <t xml:space="preserve">summary card read "Card (0)" with a non-zero amount</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Axis labels lose their suffix</t>
+          <t xml:space="preserve">Trends periodic stats returns 400</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT-LOAD-11</t>
+          <t xml:space="preserve">PT-NEG-01</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">left axis ticks are bare numbers</t>
+          <t xml:space="preserve">HTTP 400 "Merchant not exists", no message shown</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right-hand axis never renders</t>
+          <t xml:space="preserve">Gateway falls back to ACH layout</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT-LOAD-10</t>
+          <t xml:space="preserve">PT-NEG-11</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">configured with a fixed domain but not drawn</t>
+          <t xml:space="preserve">portal header showed the real gateway but the legend rendered Ach+Card</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sub-heading year is fixed</t>
+          <t xml:space="preserve">Axis labels lose their suffix</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT-NEG-04</t>
+          <t xml:space="preserve">PT-LOAD-11</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shows the current year while displaying previous-year data</t>
+          <t xml:space="preserve">left axis ticks are bare numbers</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Right-hand axis never renders</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT-LOAD-10</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">configured with a fixed domain but not drawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sub-heading year is fixed</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT-NEG-04</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shows the current year while displaying previous-year data</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Chart ceiling defaults to 300</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PT-NEG-05</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">every empty account topped out at exactly 300</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submit is never disabled, in any state</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PS-SUB-02</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the component declares isSubmitButtonDisabled and updates it in five places, but index.js:606 has the line commented out - // disabled={isSubmitButtonDisabled}. The merchant gets no warning that a range is unusable until after they click</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">First click after page load is swallowed</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PS-SUB-01 / PS-SUB-04</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">press Submit or the refresh icon once on a freshly loaded page and nothing happens - no request, no spinner. Press again and it works. Measured: click 1 nothing, click 2 HTTP 200, click 3 HTTP 200. Isdateset starts true; the handler clears it and checks it on the next line, before React has applied the change. Any second interaction is enough - a date edit is NOT required. One fix clears both, and PS-LOAD-10 shares the same gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every request carries the same identifier</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PS-SUB-08</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clientRequestId is hard-coded to 1647602068707 in apis/payment.js:101, so no two calls can be told apart in logs</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date picker silently rewrites invalid input</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PS-DATE-09</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typing 13/45/2026 leaves 03/04/2026 in the field and abcd leaves the previous date, with no message. Nothing malformed reaches the API, but a merchant can query a date they never typed</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Future dates are rejected with no message</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PS-DATE-02</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a future date is accepted by the field, then Submit silently does nothing - no toast, no hint. An inverted range DOES show a toast, so the two rejections behave inconsistently</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Switching sub-merchant does not reload the stats</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PS-LOAD-10</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the dropdown and the store both change, but no payment_stats_us request is sent and the table keeps showing the previous sub-merchant figures. Verified on IPG: switched 44052731 to 44052728, zero requests, identical rows. The refetch effect is gated on !Isdateset and the mount effect has already set it true</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-17 IPG: Ctrl+A then Delete empties From Date, which falls back to showing 'MM/DD/YYYY hh:mm aa'. The table kept its data and Submit is NOT disabled (that is PS-SUB-02). OPEN QUESTION, PARKED 2026-09-17 - the expected result as written may be wrong. It says no request is sent with an empty date. In a page state where Submit is live, a request IS sent, and it carries the PREVIOUS date rather than an empty one: the field showed the placeholder while the request went out with fromDate=2026-08-01. The picker's onChange bails on a null value (index.js:546) so the stored date is never cleared - the merchant sees a blank box but gets figures for a range they cannot see. Whether no request is sent depends on whether Submit is live, which is the PS-SUB-01 gate. Case and test both left as they are for now.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG: Ctrl+A then Delete empties From Date, which falls back to showing 'MM/DD/YYYY hh:mm aa'. The table kept its data and Submit is NOT disabled (that is PS-SUB-01). OPEN QUESTION, PARKED 2026-09-17 - the expected result as written may be wrong. It says no request is sent with an empty date. In a page state where Submit is live, a request IS sent, and it carries the PREVIOUS date rather than an empty one: the field showed the placeholder while the request went out with fromDate=2026-08-01. The picker's onChange bails on a null value (index.js:546) so the stored date is never cleared - the merchant sees a blank box but gets figures for a range they cannot see. Whether no request is sent depends on whether Submit is live, which is the same Isdateset gate that makes the first click after page load do nothing. Case and test both left as they are for now.</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-SUB-02</t>
+          <t xml:space="preserve">PS-SUB-01</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-02
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-01
 Clears From Date and asserts Submit is disabled, then inverts the range and asserts the same. Marked test.fail(): the button is never disabled because index.js:606 has the disabled prop commented out.</t>
         </is>
       </c>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-SUB-03</t>
+          <t xml:space="preserve">PS-SUB-02</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-03
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-02
 Widens the window to six months and submits, then clicks refresh and asserts both dates return to the default 30-day window, the icon spins, and the table reloads with no more payments than the wider window held.</t>
         </is>
       </c>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-SUB-04</t>
+          <t xml:space="preserve">PS-SUB-03</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
         <is>
           <t xml:space="preserve">1. Open Payment Stats from the sidebar and let the data load fully
 2. Click the refresh icon ONCE
-3. Verify it does NOT animate - the first click after page load is swallowed (see PS-SUB-01, same cause)
+3. Verify it does NOT animate - the first click after the page loads is swallowed
 4. Click the refresh icon a SECOND time
 5. Verify it now animates while the data reloads
 6. Verify the animation stops once the figures come back
@@ -2339,7 +2339,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-04
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-03
 Lets the page settle, clicks refresh and asserts the icon starts spinning. Marked test.fail(): on a freshly loaded page refresh does nothing at all.</t>
         </is>
       </c>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-17 IPG, DEFECT CONFIRMED, wording corrected after re-measurement. The refresh icon is not dead - it ignores exactly one click, the first after page load. Sampling the icon class every 40ms: click 1 never span and sent no request, click 2 span and returned HTTP 200, click 3 the same. An earlier note said it 'only works once a Submit has run' - that is wrong, a second refresh click is enough on its own. Same !Isdateset gate as PS-SUB-01, and one fix clears both.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG, DEFECT CONFIRMED, wording corrected after re-measurement. The refresh icon is not dead - it ignores exactly one click, the first after page load. Sampling the icon class every 40ms: click 1 never span and sent no request, click 2 span and returned HTTP 200, click 3 the same. An earlier note said it 'only works once a Submit has run' - that is wrong, a second refresh click is enough on its own. The cause is the !Isdateset gate: the handler clears the flag and then reads it on the next line, before React has applied the change.</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-SUB-05</t>
+          <t xml:space="preserve">PS-SUB-04</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-05
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-04
 Expands Prepare Query on BillPay, confirms Select, Group and Having plus Execute and Cancel, then asserts refresh collapses the panel and leaves the default columns intact.</t>
         </is>
       </c>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-SUB-06</t>
+          <t xml:space="preserve">PS-SUB-05</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-06
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-05
 Trims the Select list to two fields and executes, asserts the table narrows to those plus Amount and Count and that a dropped column really left, then asserts refresh restores the full default set.</t>
         </is>
       </c>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-SUB-07</t>
+          <t xml:space="preserve">PS-SUB-06</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-07
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-06
 Records the figures for a 3-day and a 90-day range separately, then fires the 90-day query and switches to the 3-day range without waiting, so two different queries are in flight at once. Asserts the newest one wins. Replaces an earlier version that clicked Submit three times on the SAME range - every request asked for the same figures, so it could never fail.</t>
         </is>
       </c>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-SUB-08</t>
+          <t xml:space="preserve">PS-SUB-07</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-08
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-SUB-07
 Collects clientRequestId from two separate calls and asserts they differ. Marked test.fail(): the value is hard-coded. One of only three network reads in the module - the parameter has no UI surface.</t>
         </is>
       </c>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-LOAD-06 (flag=SUCCESS), PS-SUB-08 (clientRequestId) and PT-LOAD-07 (pageNumber). Each is a query parameter that is never displayed, never configurable and leaves no visible trace, so the screen genuinely cannot answer the question. Every other case is checked on screen</t>
+          <t xml:space="preserve">PS-LOAD-06 (flag=SUCCESS), PS-SUB-07 (clientRequestId) and PT-LOAD-07 (pageNumber). Each is a query parameter that is never displayed, never configurable and leaves no visible trace, so the screen genuinely cannot answer the question. Every other case is checked on screen</t>
         </is>
       </c>
     </row>
@@ -16518,7 +16518,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-SUB-02</t>
+          <t xml:space="preserve">PS-SUB-01</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-SUB-04</t>
+          <t xml:space="preserve">PS-SUB-03</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-SUB-08</t>
+          <t xml:space="preserve">PS-SUB-07</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS-COL-01</t>
+          <t xml:space="preserve">PS-COL-01,02</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3062,10 +3062,15 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N29" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-COL-04
+Asserts SnapPay's five request-breakdown columns are present and that neither IPG's Type nor BillPay's Funding Method leaks in. Order is not asserted.</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -3163,10 +3168,15 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N30" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-COL-05 (2 tests)
+Widens the window to 90 days, then asserts all eight payment categories appear, none is repeated, and categories with no activity are still listed. Runs on IPG and CommerceHub - BillPay and SnapPay have no Type column.</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Corrected after run</t>
@@ -15483,7 +15493,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -15534,7 +15544,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109</t>
+          <t xml:space="preserve">107</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -2595,7 +2595,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repeated Submit clicks do not stack duplicate requests</t>
+          <t xml:space="preserve">When two queries overlap, the newest result is the one left on screen</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3271,10 +3271,15 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N31" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-COL-06 (2 tests)
+Asserts Amount(%) and Qty(%) each total 100 within rounding tolerance, and that no individual row falls outside 0-100. IPG and CommerceHub only - the other gateways have no percentage columns.</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Corrected after run</t>
@@ -3367,10 +3372,15 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N32" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-COL-07 (3 tests)
+Asserts every Amount cell matches the currency shape and no cell is blank. Runs one gateway per column layout - IPG, BillPay and SnapPay - so the claim is proven independent of the column set.</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -3463,10 +3473,15 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N33" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-COL-08 (2 tests)
+Asserts every header reports aria-sort='none', then clicks two headers and asserts the row order is unchanged and no sorted state appears.</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -3561,10 +3576,14 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N34" s="2"/>
+          <t xml:space="preserve">Blocked</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs an India merchant. credentials/qa.json has the india account active:false - 'India region - not tested' - so there is nothing to log in with.</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Blocked</t>
@@ -3658,10 +3677,15 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N35" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-01 (6 tests)
+Asserts the panel is offered to BillPay, SnapPay and MerchantE and absent on IPG, CommerceHub and NuveiPaya. Both directions matter - proving a gateway does NOT offer it is half the case.</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -3755,10 +3779,15 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N36" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-02
+Asserts the panel starts collapsed, opens on click showing Select, Group, Having, Execute and Cancel, closes again, and that the chevron flips each way. The chevron is found by walking out from the label text - the page carries several expand chevrons and a plain selector reads the wrong one.</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -3852,10 +3881,15 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N37" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-03
+Asserts BillPay opens with all four funding fields already chosen and offers no others. The dropdown hides what is already selected, so the field is cleared first to enumerate the full list.</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -3949,10 +3983,15 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N38" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-04
+Same for SnapPay: Request Type, Channel, transaction Amount and Fee Amount.</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -4047,10 +4086,15 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N39" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-05
+Asserts emptying Select locks Group, Having and Execute, and that putting a field back frees Group. NOTE Having and Execute do NOT recover at that point - they stay locked until Group itself is touched. Asserted as it behaves, with a comment, so the partial recovery is recorded rather than mistaken for a flake.</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -4145,10 +4189,15 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N40" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-06
+Asserts emptying Group locks Having and Execute while Select stays populated, and that both recover as soon as a Group field goes back.</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -4243,10 +4292,15 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N41" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-07
+Asserts a text field - Funding Method and Channel - offers exactly 'is equal to' and 'is not equal to' and nothing else.</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -4341,10 +4395,15 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N42" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-08
+Asserts an amount field offers all six operators, and that the value control becomes a typed box rather than a dropdown. The swap shows up as one fewer autocomplete on the page, which is the on-screen signal.</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -4439,10 +4498,15 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N43" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-09
+Asserts And/Or stays locked with the Having row empty, with only a field chosen, and with a field and operator but no value - then unlocks once all three are set.</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Verified</t>
@@ -4538,10 +4602,15 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N44" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-10
+Trims Select to two fields and executes, asserting the table rebuilds around those plus Amount and Count and that a dropped field is gone. Chips are removed individually rather than clearing the field, because emptying Select disables Execute and it does not recover - see PS-PQ-05.</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
@@ -4637,10 +4706,15 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N45" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-11
+Builds a Having clause on a value present in the data, executes, and asserts every returned row satisfies it and that the result is smaller than before. Checked on screen: a clause that works shows itself in the rows.</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
@@ -4736,10 +4810,15 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N46" s="2"/>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-12
+Narrows the query, executes, then asserts Cancel restores the columns and the date range and closes the panel.</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
@@ -4835,10 +4914,15 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="N47" s="2"/>
+          <t xml:space="preserve">Automated (expected fail)</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-analytics.spec.ts :: @PS-PQ-13
+Asserts that Execute after Cancel queries what the panel is showing. Marked test.fail(): Cancel restores the display but not the query state, so Execute re-sends the narrowed selection and a column disappears with nothing to explain it.</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
@@ -4933,13 +5017,13 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -4959,7 +5043,7 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 SnapPay: pressing Execute with the DEFAULT chips sent select_fields and groupby_fields identically as 'request_type,channel,transaction_amount,fee_amount' - no mismatch on this path. The risk only arises if the amount field is removed and re-added from the Select dropdown, which re-reads a different option list. Re-test by removing and re-adding 'transaction Amount' before pressing Execute.</t>
+          <t xml:space="preserve">QA 2026-09-21 SnapPay: no defect. Pressing Execute with the default chips sends select_fields and groupby_fields identically as request_type,channel,transaction_amount,fee_amount, and the resulting Amount column is populated. Automated as a regression guard. Step 9 is the only part needing the network: the two parameter names have no surface on the page.</t>
         </is>
       </c>
     </row>
@@ -5043,13 +5127,13 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated (expected fail)</t>
         </is>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5067,7 +5151,11 @@
           <t xml:space="preserve">PaymentAnalytics/index.js:418-431</t>
         </is>
       </c>
-      <c r="S49" s="2"/>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QA 2026-09-21. All six combinations a-f automated. SnapPay passes all six. BillPay DEFECT - an executed query is affected by the queries executed before it. In one session: displayed_fee_amount&gt;'2.5' run first returned 6 rows with $2.50 correctly excluded; the same clause run after two Funding Method clauses returned 7 rows including a $2.50 row. having_fields, select_fields and groupby_fields were byte-identical across both executes, and displayed_fee_amount is a group key rather than an aggregate, so the $2.50 is the literal fee and not a rounded total. Marked expected-fail on BillPay only; because it fails at combination (c), combinations d, e and f are not exercised on BillPay until this is fixed. The case names four gateways but only two can run it: MerchantE's panel is inert (PS-PQ-16) and NuveiPay has no panel (PS-PQ-01). The panel labels the operator 'is less than and equal to', not 'or equal to'.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2">
@@ -5140,13 +5228,13 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated (expected fail)</t>
         </is>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -5164,7 +5252,11 @@
           <t xml:space="preserve">PaymentAnalytics/index.js:618-646</t>
         </is>
       </c>
-      <c r="S50" s="2"/>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QA 2026-09-21 DEFECT - MerchantE's Prepare Query panel is present and populated but inert. Trimming Select from four fields to two and pressing Execute left the columns and every row byte-identical (Type, Amount, Amount(%), Qty, Qty(%)). The request goes out carrying the narrowed select_fields and returns 200, so the query runs; the page renders the standard payment-type breakdown and ignores the result. The case's original premise, that MerchantE returns an error, no longer holds. The account also has no payments in the window, so every row reads $0.00.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2">
@@ -5231,7 +5323,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N51" s="2"/>
@@ -5257,7 +5349,7 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: the 'Payment Statistics' graph heading rendered on all four gateways.</t>
+          <t xml:space="preserve">QA 2026-09-21 PASS. Heading 'Payment Statistics' renders and every bar carries a percentage caption and a drawn width. Gateway note: the Payment Stats table has two shapes. Gateways WITHOUT Prepare Query (IPG, CommerceHub, NuveiPay) render the fixed payment-type breakdown - Type, Amount, Amount(%), Qty, Qty(%) - which is what the graph is drawn from. Gateways WITH Prepare Query (BillPay, SnapPay) render the grouped query result instead and have no Qty(%) column at all. Automated on IPG, which has the breakdown table and real activity. MerchantE has the breakdown table but no payments, so it draws no bars.</t>
         </is>
       </c>
     </row>
@@ -5327,13 +5419,13 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -5353,7 +5445,7 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-21 PASS. On IPG the table lists 8 payment types, 2 with activity (Card Payments, Card Voids), and the graph draws exactly 2 bars with those labels. Gateway note: the Payment Stats table has two shapes. Gateways WITHOUT Prepare Query (IPG, CommerceHub, NuveiPay) render the fixed payment-type breakdown - Type, Amount, Amount(%), Qty, Qty(%) - which is what the graph is drawn from. Gateways WITH Prepare Query (BillPay, SnapPay) render the grouped query result instead and have no Qty(%) column at all. Automated on IPG, which has the breakdown table and real activity. MerchantE has the breakdown table but no payments, so it draws no bars.</t>
         </is>
       </c>
     </row>
@@ -5424,13 +5516,13 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -5450,7 +5542,7 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-21 PASS. Each bar's printed percentage equals its table row's Qty(%), and the bar's inline width equals that same percentage. Card Payments dominates at 99.04% and has the widest bar; Card Voids at 0.96% is proportionally narrow. Gateway note: the Payment Stats table has two shapes. Gateways WITHOUT Prepare Query (IPG, CommerceHub, NuveiPay) render the fixed payment-type breakdown - Type, Amount, Amount(%), Qty, Qty(%) - which is what the graph is drawn from. Gateways WITH Prepare Query (BillPay, SnapPay) render the grouped query result instead and have no Qty(%) column at all. Automated on IPG, which has the breakdown table and real activity. MerchantE has the breakdown table but no payments, so it draws no bars.</t>
         </is>
       </c>
     </row>
@@ -5520,13 +5612,13 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -5546,7 +5638,7 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-21 PASS. On IPG 6 of the 8 payment types have zero quantity; none of them is drawn in the graph, and all 6 remain listed in the table. Gateway note: the Payment Stats table has two shapes. Gateways WITHOUT Prepare Query (IPG, CommerceHub, NuveiPay) render the fixed payment-type breakdown - Type, Amount, Amount(%), Qty, Qty(%) - which is what the graph is drawn from. Gateways WITH Prepare Query (BillPay, SnapPay) render the grouped query result instead and have no Qty(%) column at all. Automated on IPG, which has the breakdown table and real activity. MerchantE has the breakdown table but no payments, so it draws no bars.</t>
         </is>
       </c>
     </row>
@@ -5617,13 +5709,13 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -5643,7 +5735,7 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-21 PASS. Changing the range from the last 90 days to the preceding year updates the table figures, and the redrawn bars match the new table exactly - same names, same percentages, nothing left over from the previous range. Gateway note: the Payment Stats table has two shapes. Gateways WITHOUT Prepare Query (IPG, CommerceHub, NuveiPay) render the fixed payment-type breakdown - Type, Amount, Amount(%), Qty, Qty(%) - which is what the graph is drawn from. Gateways WITH Prepare Query (BillPay, SnapPay) render the grouped query result instead and have no Qty(%) column at all. Automated on IPG, which has the breakdown table and real activity. MerchantE has the breakdown table but no payments, so it draws no bars.</t>
         </is>
       </c>
     </row>
@@ -5729,13 +5821,13 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated (expected fail)</t>
         </is>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -5753,7 +5845,11 @@
           <t xml:space="preserve">PaymentAnalytics/index.js:185-202,362-404</t>
         </is>
       </c>
-      <c r="S56" s="2"/>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QA 2026-09-21. Automated on BillPay as two tests. PASS - regrouping re-splits the same payments: the default grouping, grouping by Funding Method alone, and the two-field grouping all return 95 ACH and 121 card payments. A Having clause of funding_method!='ACH' narrows the table from 7 rows to 6, removes every ACH row, and leaves the graph untouched. DEFECT (expected-fail test) - the graph and the query table disagree about the same payments over the same range. The query counts 95 ACH against 121 card, a 43.98% ACH share, while the graph draws ACH at 44.81%. Working back from 44.81% the graph is counting 95 ACH and 117 card payments - four fewer card payments than the query finds. The query side is self-consistent across all three groupings, so the disagreement is between the two views, not within the query. Reproduced on both repeats. The case names four gateways; only BillPay can run it. SnapPay's query table holds card activity only (Category is CardSale throughout) so the precondition of a range with both card and ACH activity is not met. MerchantE's query panel is inert (PS-PQ-16). NuveiPay has no query panel (PS-PQ-01).</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2">
@@ -5824,7 +5920,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated (expected fail)</t>
         </is>
       </c>
       <c r="N57" s="2"/>
@@ -5850,7 +5946,7 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: CONFIRMED LIVE on all four gateways. payment_stats_us returned HTTP 400 every time and the page showed no toast, no banner and no inline message - just an empty table under correct headers. Indistinguishable from a quiet date range.</t>
+          <t xml:space="preserve">QA 2026-09-21 DEFECT CONFIRMED by automation. With payment_stats_us blocked, the table renders its five headers with no rows, the refresh icon is not spinning, and there is no toast, banner or inline message of any kind. A broken request is indistinguishable from a date range that had no payments. Test asserts that something tells the user, marked expected-fail until it does.</t>
         </is>
       </c>
     </row>
@@ -5927,7 +6023,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated (expected fail)</t>
         </is>
       </c>
       <c r="N58" s="2"/>
@@ -5953,7 +6049,7 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 BillPay: CONFIRMED - the browser console shows 'err is not defined' alongside the 400. The failure handler throws its own ReferenceError, so the real API error never reaches the console. Also seen: repeated 'Invalid value used as weak map key' page errors.</t>
+          <t xml:space="preserve">QA 2026-09-21 DEFECT CONFIRMED by automation. The stats call is failed with a real HTTP 500 so the page's own failure handler runs, and the console then carries the handler's ReferenceError 'err is not defined' instead of the API error that caused it. Support is left with nothing to diagnose. Invisible in normal use - a healthy session never enters the handler.</t>
         </is>
       </c>
     </row>
@@ -6026,13 +6122,13 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -6052,7 +6148,7 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised.</t>
+          <t xml:space="preserve">QA 2026-09-21 PASS. A 401 on the stats call returns the merchant to the sign-in form, clears the stored token, and the browser Back button does not restore the authenticated page. NOTE the 401 is simulated, as the case prescribes: corrupting the stored token does NOT produce one - measured, the server answers a malformed token with 400, and on that path the page keeps its stale rows and says nothing (see PS-NEG-01).</t>
         </is>
       </c>
     </row>
@@ -6125,13 +6221,13 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Blocked</t>
         </is>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Blocked</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -6151,7 +6247,7 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-21 BLOCKED - the Transactions grid's Date &amp; Time column filter does not filter. Measured on sub-merchant 44052730 (29,069 transactions), driving the popover directly: the date box wants YYYY-MM-DD rather than the MM/DD/YYYY the grid displays; typing 2026-09-19 lands correctly and Search does enable; but 'is equal to', 'greater than or equal to' and 'less than or equal to' each returned the full 29,069 rows, still showing 9/21 dates the filter should have excluded. Without a working date filter the comparison is a single day on one page against every transaction ever on the other, which proves nothing. SEPARATELY WORTH RAISING: Payment Stats defaults to sub-merchant 44052731 and reports card payments under it, while All Transactions lists nothing at all for that same sub-merchant; any reconciliation must pin both pages to 44052730.</t>
         </is>
       </c>
     </row>
@@ -6222,13 +6318,13 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -6248,7 +6344,7 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-21 PASS. The Payment Trends tooltip for the newest month and Payment Stats for that same month agree on both the Card and the ACH count. Reading the chart needed two things worth knowing: the columns grow from zero height when the chart draws itself, so measuring too early reports every bar as 0 tall; and the chart is assembled from several SVGs, with a background rect and a zero-height rect for every series that has no activity.</t>
         </is>
       </c>
     </row>
@@ -6320,13 +6416,13 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -6346,7 +6442,7 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-21 PASS on CommerceHub, which has card activity and nothing else - exactly the single-active-type window this case needs. Card Payments reads 100 in both percentage columns, every other row reads a real 0 rather than a blank or a dash, and the graph draws one bar at 100% width.</t>
         </is>
       </c>
     </row>
@@ -6416,13 +6512,13 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -6442,7 +6538,7 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-21 PASS. A range in 2019 with no payments renders a clean 0 in every Amount(%) and Qty(%) cell - no NaN, no Infinity, no blanks - and the graph draws its frame with no bars rather than disappearing or crashing.</t>
         </is>
       </c>
     </row>
@@ -6514,13 +6610,13 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -6540,7 +6636,7 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-21 PASS on IPG. A two-year range returns and renders the table and the graph, with the page still responding. Elapsed time is asserted under 60s so a slide into minutes fails the build.</t>
         </is>
       </c>
     </row>
@@ -6611,13 +6707,13 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -6637,7 +6733,7 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-21 PASS on BillPay. Regrouping to a single field re-splits the same payments without changing the overall Count total. Totals are summed over EVERY row by scrolling the grid - it paints only the rows that fit the viewport, so adding up what is on screen quietly undercounts.</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6805,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N66" s="2"/>
@@ -6735,7 +6831,7 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 SnapPay: navigating to Payment Trends and back reset the From Date to the default 30-day window and left the Prepare Query panel collapsed - a clean state with no leftovers.</t>
+          <t xml:space="preserve">QA 2026-09-21 PASS on SnapPay. Going to Payment Trends and back resets the dates to the default window, refetches, leaves the Prepare Query panel collapsed and logs no console error. NOTE this case exposed a bug in the shared SideMenu page object: moving between two pages in the SAME sidebar group clicked the group header again and collapsed it, so the submenu animated away mid-click. Now guarded to only open a group that is not already open.</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6906,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated (expected fail)</t>
         </is>
       </c>
       <c r="N67" s="2"/>
@@ -6836,7 +6932,7 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: CONFIRMED, and the trigger is a page refresh - NOT every request as first recorded. Navigating to Payment Stats from the sidebar sends a populated sub_merchant_id and the table renders normally. Pressing F5 on that same page re-sends it EMPTY, the backend returns 400 and the table empties with no error shown. Confirmed independently by the user in a normal browser session.</t>
+          <t xml:space="preserve">QA 2026-09-21 DEFECT CONFIRMED by automation. Reaching Payment Stats through the sidebar sends a populated sub_merchant_id and the table renders. Pressing F5 on that same page re-sends the request with an EMPTY sub_merchant_id, the API answers 400 and the table empties - with nothing shown to the user, because the page fails silently (PS-NEG-01).</t>
         </is>
       </c>
     </row>
@@ -6911,13 +7007,13 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated (expected fail)</t>
         </is>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -6937,7 +7033,7 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cannot be observed today - September builds a valid date by luck. Must be run in October, November or December, or with the machine clock moved forward.</t>
+          <t xml:space="preserve">QA 2026-09-21 DEFECT CONFIRMED, and it is no longer only a suspicion. Automated as three tests, one per month, by moving the browser clock. The default range is built by string concatenation with a FIXED leading zero, so month 10 becomes '010'. Captured from the request: October toDate '2026-010-15 10:00:00'; November fromDate '2026-010-21 00:00:00'; December fromDate '2026-011-5 00:00:00' (also a single-digit day). The date PICKERS show perfectly valid dates throughout - 09/15/2026, 10/21/2026 - so nothing looks wrong on screen; only the request carries the malformed value. Method note: the clock must be moved AFTER the page is open and the range rebuilt with the refresh icon. Moving it before navigation freezes animations so the sidebar never settles, and the refresh must be clicked twice because the first click is swallowed (PS-SUB-03).</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15589,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -15510,7 +15606,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -15544,7 +15640,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -1512,7 +1512,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-22 PASS. Changing the From Date and pressing Submit refetches: the pickers hold the new range and both the table and the graph redraw to match it.</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-22 PASS on BillPay. Trimming Select to two fields and pressing Execute rebuilds the table around exactly those fields plus Amount and Count; the dropped fields disappear as columns and the rows regroup, so fewer rows carry larger counts. Proven on screen - the DevTools step is not needed, since a query that reaches the API wrongly shows up in the table.</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-22 PASS on BillPay. A Having clause of Funding Method is equal to a value present in the data returns only rows carrying that value, and fewer rows than the unfiltered table. Proven on screen rather than by reading having_fields: a clause that works shows itself in the rows, which is what the merchant relies on.</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-22 PASS on BillPay. Cancel collapses the panel, restores the default columns and puts the default date range back.</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not exercised in this run. NOTE: this case IS testable today - reach Payment Stats by clicking through the sidebar, not by opening the URL directly. A direct load or refresh drops the sub-merchant id and returns 400 (see PS-NEG-11), which is what my probes hit.</t>
+          <t xml:space="preserve">QA 2026-09-22 DEFECT CONFIRMED, behaves as recorded. Cancel restores what is DISPLAYED but not the underlying query state, so an Execute straight after Cancel sends the query the panel no longer shows. Test asserts the intended behaviour and is marked expected-fail.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -4658,7 +4658,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Having clause is sent to the API in the expected form</t>
+          <t xml:space="preserve">Having clause is applied to the rows, singly and when two are joined</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -4669,24 +4669,26 @@
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Having: Funding Method is equal to a value present in the data
-Expected having_fields form: field then operator then the quoted value
+Second condition: another field, joined with And
+The clause is judged by the rows it returns, not by the request - a clause that reaches the backend wrongly shows up as wrong rows
 Gateway: BillPay</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Payment Stats as BillPay and expand Prepare Query
-2. Build a Having clause of 'Funding Method' 'is equal to' and a value you can see in the table
-3. Click Execute
-4. In DevTools inspect the having_fields query parameter
-5. Verify it carries the field name, the operator and the value in quotes
-6. Verify the returned rows all satisfy that condition
-7. Add a second condition joined by And and verify both appear in having_fields</t>
+2. Note the values shown in the Funding Method column and how many rows there are
+3. Build a Having clause of 'Funding Method' 'is equal to' a value you can see in the table
+4. Click Execute
+5. Verify every returned row carries that value and nothing else
+6. Verify the result is smaller than the unfiltered table, and not empty
+7. Choose And and add a second condition on a different field
+8. Click Execute and verify every row satisfies BOTH conditions</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Having clause reaches the API in the documented form and the returned rows all satisfy it, including when two conditions are joined</t>
+          <t xml:space="preserve">Each Having condition is applied to the rows returned, and two conditions joined by And return only the rows that satisfy both</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5178,28 +5180,29 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MerchantE Prepare Query returns data once its merchant record is fixed</t>
+          <t xml:space="preserve">MerchantE Prepare Query panel drives the table</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MerchantE customer-portal user authenticated; Payment Analytics group visible in sidebar; Payment Stats page reachable; MerchantE credentials that resolve to a working merchant record</t>
+          <t xml:space="preserve">MerchantE customer-portal user authenticated; Payment Analytics group visible in sidebar; Payment Stats page reachable</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MerchantE offers Prepare Query (it is in the SnapPay-like group)
 Select field options: Request Type, Channel, transaction Amount, Fee Amount
-Blocked until MerchantE stops returning an error on QA - see PT-NEG-01
+The earlier premise that MerchantE returns an error no longer holds - the stats request answers 200 and the panel is fully populated. What it does not do is act on anything.
+The account has no payments in the window, so every row reads $0.00 - judge this case by whether the COLUMNS change, not by the figures
 Gateway: MerchantE</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Log in as the MerchantE merchant and open Payment Stats
-2. Verify the stats request returns 200, not an error
-3. Verify the table renders payment-type rows with real figures
-4. Expand Prepare Query and verify the Select list offers Request Type, Channel, transaction Amount and Fee Amount
+          <t xml:space="preserve">1. Log in as the MerchantE merchant and open Payment Stats from the sidebar
+2. Verify the stats request returns 200 and the table renders its payment-type rows
+3. Expand Prepare Query and verify the Select list offers Request Type, Channel, transaction Amount and Fee Amount
+4. Note the column headings currently shown in the table
 5. Reduce Select to two fields and click Execute
 6. Verify the table rebuilds with only those fields plus Amount and Count
 7. Build a Having clause and Execute - verify only matching rows come back
@@ -5208,7 +5211,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MerchantE loads its stats and its Prepare Query behaves like the other query gateways. While the merchant record is broken this case cannot run - record it as blocked rather than failed</t>
+          <t xml:space="preserve">MerchantE's Prepare Query behaves like the other query gateways: trimming Select changes the columns, a Having clause narrows the rows, and Cancel puts the defaults back</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -4868,35 +4868,36 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Executing immediately after Cancel does not send an empty grouping</t>
+          <t xml:space="preserve">Execute straight after Cancel queries what the panel shows</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BillPay customer-portal user authenticated; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Network tab open</t>
+          <t xml:space="preserve">BillPay customer-portal user authenticated; Payment Analytics group visible in sidebar; Payment Stats page reachable</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">After Cancel the Group list is left empty internally
-Action: press Execute straight after Cancel without re-picking fields
+          <t xml:space="preserve">Action: press Execute straight after Cancel without re-picking any field
+Cancel restores what is DISPLAYED but not the query behind it, so the panel and the result disagree
+Judged by the column headings - the panel shows every field selected while the table comes back missing the ones trimmed before Cancel
 Gateway: BillPay</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Payment Stats as BillPay and expand Prepare Query
-2. Run any Execute, then click Cancel
-3. Without choosing any field again, inspect the Group control
-4. Press Execute
-5. In DevTools inspect groupby_fields on the outgoing request
-6. Verify it is not sent empty, and that the table does not break
-7. Record what the API returns if an empty grouping is sent</t>
+          <t xml:space="preserve">1. Open Payment Stats as BillPay and note the column headings shown
+2. Expand Prepare Query, remove one field from Select and click Execute
+3. Verify the table narrows - that column is gone
+4. Click Cancel and verify the original column headings come back
+5. Expand Prepare Query again and verify Select shows EVERY field selected
+6. Without changing anything, press Execute
+7. Compare the column headings against step 1 - they must match, because that is what the panel is showing</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Execute straight after Cancel must not send an empty grouping or produce a broken table. Record the request and response if it does (defect, log it)</t>
+          <t xml:space="preserve">Execute after Cancel queries the fields the panel is displaying. If the table comes back missing the field trimmed before Cancel, the panel and the query disagree and the merchant is shown a result they did not ask for (defect, log it)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -4559,7 +4559,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BillPay customer-portal user authenticated; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Network tab open</t>
+          <t xml:space="preserve">BillPay customer-portal user authenticated; Payment Analytics group visible in sidebar; Payment Stats page reachable</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -4571,18 +4571,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Payment Stats as BillPay and expand Prepare Query
-2. Reduce Select to 'Funding Method' and 'Channel' only
-3. Click Execute
-4. In DevTools verify the request carries select_fields and groupby_fields matching your choices
+          <t xml:space="preserve">1. Open Payment Stats as BillPay and note the column headings and the total of the Count column
+2. Expand Prepare Query
+3. Reduce Select to 'Funding Method' and 'Channel' only
+4. Click Execute
 5. Verify the table now shows only Funding Method, Channel, Amount and Count
 6. Verify the removed fields no longer appear as columns
-7. Verify the row values regroup to match the reduced grouping</t>
+7. Verify the rows regroup - one row per Funding Method and Channel pair, so fewer rows carry larger counts
+8. Verify the Count column still totals the same as step 1, since the same payments are being split a different way</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Execute sends the chosen fields to the API and rebuilds the table to show only those fields plus Amount and Count</t>
+          <t xml:space="preserve">Execute rebuilds the table around the chosen fields plus Amount and Count, the dropped fields disappear as columns, and the rows regroup without changing the overall total</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -4663,7 +4664,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BillPay customer-portal user authenticated; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Network tab open</t>
+          <t xml:space="preserve">BillPay customer-portal user authenticated; Payment Analytics group visible in sidebar; Payment Stats page reachable</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -8282,12 +8283,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selecting 'Last 3 Months' redraws the chart with 3 months and re-calls the API</t>
+          <t xml:space="preserve">Selecting 'Last 3 Months' redraws the chart with 3 months</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Trends page reachable; DevTools Network tab open</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Trends page reachable</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -8300,17 +8301,18 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Payment Trends (defaults to Last 6 Months)
+          <t xml:space="preserve">1. Open Payment Trends (defaults to Last 6 Months) and count the X-axis labels - expect 6
 2. Open the dropdown and select 'Last 3 Months'
 3. Wait for the chart to redraw
-4. Count the X-axis labels
+4. Count the X-axis labels - expect exactly 3
 5. Verify the right-most label is still the current month
-6. In DevTools verify a new periodic_payment_stats_us call fired with pageSize=3</t>
+6. Verify the labels are the three most recent months, in order
+NOTE the label count IS the page size on screen - a chart drawn with 3 months is a request made for 3 months, so the request does not need to be read</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chart shows exactly 3 month labels ending at the current month and a fresh API call is made with pageSize=3</t>
+          <t xml:space="preserve">The chart redraws with exactly 3 month labels ending at the current month, which is what a fresh request for 3 months looks like on screen</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -8391,7 +8393,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Trends page reachable; DevTools Network tab open</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Trends page reachable</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -8406,15 +8408,16 @@
         <is>
           <t xml:space="preserve">1. Open Payment Trends
 2. Select 'Last 12 Months' from the dropdown
-3. Count the X-axis labels — expect 12
+3. Count the X-axis labels - expect exactly 12
 4. Verify the labels are drawn on a slant (rotated), not horizontal
 5. Verify the labels do not overlap each other
-6. In DevTools verify pageSize=12 on the new request</t>
+6. Verify the right-most label is still the current month
+NOTE the label count IS the page size on screen - a chart drawn with 12 months is a request made for 12 months, so the request does not need to be read</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 month labels are shown, rendered rotated so they stay readable, and the API is called with pageSize=12</t>
+          <t xml:space="preserve">12 month labels are shown ending at the current month, rendered rotated so they stay readable and do not overlap</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -5951,7 +5951,7 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-21 DEFECT CONFIRMED by automation. With payment_stats_us blocked, the table renders its five headers with no rows, the refresh icon is not spinning, and there is no toast, banner or inline message of any kind. A broken request is indistinguishable from a date range that had no payments. Test asserts that something tells the user, marked expected-fail until it does.</t>
+          <t xml:space="preserve">QA 2026-09-21 DEFECT CONFIRMED by automation. With payment_stats_us BLOCKED, so that no response arrives at all, the table renders its five headers with no rows, the refresh icon is not spinning, and there is no toast, banner or inline message of any kind. A broken request is indistinguishable from a date range that had no payments. Scope note added 2026-09-23: this silence applies to a blocked or failed connection. When the server DOES answer with an error, the page shows its message - see PS-NEG-11, where a 400 produces a 'sub_merchant_id is required' toast. Test asserts that something tells the user, marked expected-fail until it does.</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-21 DEFECT CONFIRMED by automation. Reaching Payment Stats through the sidebar sends a populated sub_merchant_id and the table renders. Pressing F5 on that same page re-sends the request with an EMPTY sub_merchant_id, the API answers 400 and the table empties - with nothing shown to the user, because the page fails silently (PS-NEG-01).</t>
+          <t xml:space="preserve">QA 2026-09-21 DEFECT CONFIRMED by automation, remark corrected 2026-09-23. Reaching Payment Stats through the sidebar sends a populated sub_merchant_id and the table renders. Pressing F5 on that same page re-sends the request with an EMPTY sub_merchant_id, the server answers 400 and the table empties to 'No rows'. CORRECTION: an earlier note said nothing is shown to the user. That is wrong - a red toast appears carrying the server's message, 'sub_merchant_id is required'. It is unhelpful to a merchant and leaks an internal parameter name, but it is not silence. The silent case is PS-NEG-01, where the request is blocked outright and no response arrives at all, so the page's handler never runs.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -6866,32 +6866,32 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Network tab open, filtered on payment_stats</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reach the page two ways and compare:
+          <t xml:space="preserve">Reach the page two ways and compare what is on screen:
   (a) click Payment Analytics &gt; Payment Stats in the sidebar
-  (b) press F5 on that same page, or paste the /paymentStats URL into a fresh tab
-Watch the sub_merchant_id query parameter on each request
+  (b) press F5 on that same page
+The page names the missing parameter itself in a toast, so the request does not need to be read
 Gateway: any - behaviour is identical on every gateway</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Log in and open DevTools &gt; Network, filtering on 'payment_stats'
-2. Navigate to Payment Analytics &gt; Payment Stats using the sidebar
-3. Inspect the payment_stats_us request and verify sub_merchant_id carries the id shown in the portal header
-4. Verify the response is 200 and the table renders its payment-type rows
-5. Now press F5 to refresh that same page
-6. Inspect the new payment_stats_us request and verify sub_merchant_id is still populated
-7. Verify the response is still 200 and the table still shows its rows</t>
+          <t xml:space="preserve">1. Log in and navigate to Payment Analytics &gt; Payment Stats using the sidebar
+2. Verify the table renders its rows, and note the sub-merchant shown in the selector at the top of the page
+3. Press F5 to refresh that same page
+4. Verify the table still shows its rows
+5. Verify no error toast appears
+6. Verify the sub-merchant selector still shows the same sub-merchant
+7. Navigate to the page from the sidebar again and verify the data returns</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The page must load its data whichever way it is reached. A refresh that sends an empty sub_merchant_id, returns 400 and empties the table - with no error shown to the user - is a defect (log it)</t>
+          <t xml:space="preserve">The page loads its data whichever way it is reached. A refresh that empties the table to 'No rows' and raises a 'sub_merchant_id is required' toast is a defect (log it) - the selector still shows the sub-merchant, so the page knows it and simply does not send it</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -5882,30 +5882,32 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; ability to block or fail the stats request via DevTools request blocking</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools open</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simulated failure: payment_stats_us blocked or returning 500
+          <t xml:space="preserve">Simulated failure: the stats request cannot reach the server
+Easiest way to cause it - DevTools &gt; Network &gt; change the throttling dropdown from 'No throttling' to 'Offline'. One dropdown, nothing to configure. Request blocking also works but blocks the exact URL, and the stats URL carries a toDate timestamp that changes every call, so the rule stops matching
 Expected UI today: no message of any kind
 Gateway: any - behaviour is identical on every gateway</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open DevTools and add a request-block rule for payment_stats_us
-2. Navigate to Payment Stats
-3. Watch the page while the request fails
+          <t xml:space="preserve">1. Open Payment Stats from the sidebar and let the figures load
+2. Open DevTools &gt; Network and set the throttling dropdown to 'Offline'
+3. Change a date and press Submit, so the page tries to fetch
 4. Verify the refresh icon stops spinning
-5. Verify NO error toast, banner or inline message appears
-6. Verify the table is left empty or showing stale data with no explanation
-7. Record that a failed load is indistinguishable from a range with no payments</t>
+5. Verify NO error toast, banner or inline message appears anywhere
+6. Verify what the table is left showing - it keeps the PREVIOUS figures, so the screen looks like a normal result for the new dates
+7. Set throttling back to 'No throttling' when finished
+8. Record that a failed load is indistinguishable from a successful one</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The page fails silently - a broken request looks exactly like an empty date range, leaving the user with no idea anything went wrong (defect, log it)</t>
+          <t xml:space="preserve">The page fails silently. Nothing tells the merchant the request failed, and the table keeps the figures from the previous range, so the screen reads as a normal result for dates it never loaded (defect, log it)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -5981,34 +5983,31 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Console open; ability to block or fail the stats request</t>
+          <t xml:space="preserve">Customer-portal user authenticated on any gateway; Payment Analytics group visible in sidebar; Payment Stats page reachable; DevTools Console open</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">This only shows up on a FAILED request. A healthy session never enters the failure handler,
-so the console stays clean apart from unrelated page noise ('Invalid value used as weak map key',
-which appears on every page regardless).
-To see it you must make the stats call fail - block payment_stats_us in DevTools, or use a
-merchant whose record is broken.
+          <t xml:space="preserve">This only shows up on a FAILED request. A healthy session never enters the failure handler, so the console stays clean apart from unrelated page noise ('Invalid value used as weak map key', which appears on every page regardless).
+Easiest way to cause it - DevTools &gt; Network &gt; set throttling to 'Offline', then force a request. Confirmed to reproduce it: the console carries net::ERR_INTERNET_DISCONNECTED followed by the handler's own 'err is not defined'.
 Gateway: any - behaviour is identical on every gateway</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open DevTools &gt; Console and clear it
-2. Open Payment Stats normally first and confirm the console shows no reference error - this is
-   the control, and proves the next step is caused by the failure and not by the page itself
-3. Now block the payment_stats_us request in DevTools
-4. Reload Payment Stats and let the request fail
+          <t xml:space="preserve">1. Open Payment Stats from the sidebar and let the figures load
+2. Open DevTools &gt; Console and clear it. Confirm no reference error is present - this is the control, and proves the next step is caused by the failure and not by the page
+3. In DevTools &gt; Network set the throttling dropdown to 'Offline'
+4. Change a date and press Submit, so the page tries to fetch
 5. Read the console output
-6. Verify the real API error reaches the console
-7. Note any reference error thrown by the handler itself in place of the underlying cause</t>
+6. Verify the genuine network or API error is reported
+7. Note any reference error thrown by the handler itself in place of the real cause
+8. Set throttling back to 'No throttling' when finished</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">When a stats request fails, the genuine API error must reach the console. A handler that throws its own reference error and swallows the real cause leaves support with nothing to diagnose (defect, log it). Note this is invisible during normal use - it only appears once something has already gone wrong</t>
+          <t xml:space="preserve">When a stats request fails, the genuine error must reach the console. A handler that throws its own reference error - 'err is not defined' - alongside it leaves support with the fault of the handler rather than the cause (defect, log it). Note this is invisible during normal use; it only appears once something has already gone wrong</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -5877,7 +5877,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failed stats request leaves the page silent with no error shown</t>
+          <t xml:space="preserve">A failed stats request tells the merchant something went wrong</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The page fails silently. Nothing tells the merchant the request failed, and the table keeps the figures from the previous range, so the screen reads as a normal result for dates it never loaded (defect, log it)</t>
+          <t xml:space="preserve">The page raises a message when the stats request cannot reach the server, so a failure is not mistaken for a date range that simply had no payments</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -5927,13 +5927,13 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automated (expected fail)</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified</t>
+          <t xml:space="preserve">Corrected after run</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-21 DEFECT CONFIRMED by automation. With payment_stats_us BLOCKED, so that no response arrives at all, the table renders its five headers with no rows, the refresh icon is not spinning, and there is no toast, banner or inline message of any kind. A broken request is indistinguishable from a date range that had no payments. Scope note added 2026-09-23: this silence applies to a blocked or failed connection. When the server DOES answer with an error, the page shows its message - see PS-NEG-11, where a 400 produces a 'sub_merchant_id is required' toast. Test asserts that something tells the user, marked expected-fail until it does.</t>
+          <t xml:space="preserve">QA 2026-09-24 PASS, and an earlier finding withdrawn. The page DOES raise a message: 'Something Went Wrong!' appears on both QA and dev when the connection is cut. This was recorded as a Critical silent-failure defect, which was wrong - the automated check matched only '.toastContainer .toast' while the message is a MUI Snackbar, so 'no message appeared' was true by construction rather than by observation. The locator is fixed and the test now passes. NOTE the table keeps the PREVIOUS range's figures behind the message; showing last-known data rather than blanking the screen is a product decision and is deliberately not asserted either way.</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">When a stats request fails, the genuine error must reach the console. A handler that throws its own reference error - 'err is not defined' - alongside it leaves support with the fault of the handler rather than the cause (defect, log it). Note this is invisible during normal use; it only appears once something has already gone wrong</t>
+          <t xml:space="preserve">When a stats request fails, the page's own failure handler must not throw. It currently contributes three faults of its own and nothing useful (defect, log it). The underlying cause is still visible, because the browser logs the network failure itself</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-21 DEFECT CONFIRMED by automation. The stats call is failed with a real HTTP 500 so the page's own failure handler runs, and the console then carries the handler's ReferenceError 'err is not defined' instead of the API error that caused it. Support is left with nothing to diagnose. Invisible in normal use - a healthy session never enters the handler.</t>
+          <t xml:space="preserve">QA 2026-09-24 DEFECT CONFIRMED, detail expanded from a merchant's own console. With the connection cut the handler breaks three times over: 'err: TypeError: Cannot convert undefined or null to object' (Object.keys on undefined), 'err: TypeError: Cannot read properties of undefined (reading error_code)', and 'Uncaught (in promise) ReferenceError: err is not defined'. It reaches into a response object that does not exist, because the request never completed. CORRECTION to an earlier note: the real cause is NOT lost - the browser logs net::ERR_INTERNET_DISCONNECTED itself, two lines above. The problem is that the handler adds three red lines of its own, so whoever is diagnosing has five errors to sift and none of them come from the handler doing its job. Each of the three is asserted separately so a partial fix shows as progress.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -6053,7 +6053,7 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-24 DEFECT CONFIRMED, detail expanded from a merchant's own console. With the connection cut the handler breaks three times over: 'err: TypeError: Cannot convert undefined or null to object' (Object.keys on undefined), 'err: TypeError: Cannot read properties of undefined (reading error_code)', and 'Uncaught (in promise) ReferenceError: err is not defined'. It reaches into a response object that does not exist, because the request never completed. CORRECTION to an earlier note: the real cause is NOT lost - the browser logs net::ERR_INTERNET_DISCONNECTED itself, two lines above. The problem is that the handler adds three red lines of its own, so whoever is diagnosing has five errors to sift and none of them come from the handler doing its job. Each of the three is asserted separately so a partial fix shows as progress.</t>
+          <t xml:space="preserve">QA 2026-09-24 DEFECT CONFIRMED. Verified twice and they agree: automated (connection cut in Playwright) and manually in the browser with DevTools &gt; Network &gt; Offline, with before/after screenshots. USER-VISIBLE HARM (the main point): after Submit fails, the table keeps showing the PREVIOUS results unchanged and no message appears anywhere on screen. Confirmed by comparing the two screenshots - From Date changed from 08/25/2026 to 07/24/2026, Submit pressed, request failed, and the same rows (ACH/CheckSale, DISCOVER/CreditSale, MASTERCARD/CreditSale...) are still listed. The merchant is left believing those figures answer the new date range. The only way to find out is to open DevTools. CONSOLE: the failure handler then breaks three times over: 'err: TypeError: Cannot convert undefined or null to object' (Object.keys on undefined), 'err: TypeError: Cannot read properties of undefined (reading error_code)', and 'Uncaught (in promise) ReferenceError: err is not defined'. It reaches into a response object that does not exist, because the request never completed. NOTE FOR ANYONE REPRODUCING: the first two are logged at info/log level, not error, so they carry no red icon and are invisible if the console filter is set to Errors only. The real cause is NOT lost - the browser logs net::ERR_INTERNET_DISCONNECTED itself, two lines above. Each of the three is asserted separately so a partial fix shows as progress.</t>
         </is>
       </c>
     </row>
@@ -15381,6 +15381,82 @@
       <c r="S152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not executed. These create real payments on the shared QA environment, which needs your go-ahead first. The Payment Stats half is also blocked until PS-NEG-11 is fixed - with sub_merchant_id sent empty the page returns 400 and shows no figures to compare against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PS-OBS-01</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payment Stats</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S9. Incidental Observations</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A config call fails with 400 on page load because merchantId is sent as undefined</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer-portal user signed in through the UI (not token injection); DevTools open on the Network and Console tabs from before the first request</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No fault injected. A completely healthy session.
+Gateway seen on: IPG</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open DevTools and select the Console tab, with the level filter left on Default levels
+2. Sign in to the customer portal through the sign-in form
+3. Open Payment Stats from Payment Analytics
+4. Read the console without applying any filter
+5. Switch to the Network tab and look for calls to /v1/merchant/ui_config
+6. Check the merchantId value in the query string of the first such call</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every request on a healthy page load carries a real merchant id and returns 2xx. No 400 appears in the console when nothing has gone wrong.</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Automated</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed, not confirmed</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IPG (seen); other gateways unchecked</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QA 2026-09-24 OBSERVED, NOT YET CONFIRMED AS A DEFECT - deliberately not called a bug yet. Spotted in a merchant&amp;#8217;s own DevTools console while reproducing PS-NEG-02, on a healthy page with nothing injected: "Failed to load resource: the server responded with a status of 400" against qaapi1.tillipay.com, with merchantId=undefined in the query string. WHAT IS PROVEN: the endpoint is GET /v1/merchant/ui_config?merchantId=&lt;id&gt;, and on a normal load it is called five times over, which is worth a look on its own. WHAT IS NOT PROVEN: the cause. It does NOT reproduce in automation - on repeated IPG runs the parameter always carried a real value (526971115880) and not one request failed. The difference is that the automation writes mainMerchantId into localStorage before the app starts, so the value is ready earlier than it would be after a real sign-in. That points at a start-up ordering problem, where the first ui_config call goes out before the merchant id has been set - but that is a hypothesis, not a measurement, and it should not be written up as a defect until someone has watched it happen. TO CONFIRM: sign in through the form rather than by injecting a token, watch the Network tab from the very first request, and see whether the first ui_config call carries undefined. IMPACT IF REAL: one failed config call on every fresh sign-in, and whatever ui_config drives is left to fall back on defaults. Not blocking - the page still loads and the figures are correct.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -5852,7 +5852,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-21. Automated on BillPay as two tests. PASS - regrouping re-splits the same payments: the default grouping, grouping by Funding Method alone, and the two-field grouping all return 95 ACH and 121 card payments. A Having clause of funding_method!='ACH' narrows the table from 7 rows to 6, removes every ACH row, and leaves the graph untouched. DEFECT (expected-fail test) - the graph and the query table disagree about the same payments over the same range. The query counts 95 ACH against 121 card, a 43.98% ACH share, while the graph draws ACH at 44.81%. Working back from 44.81% the graph is counting 95 ACH and 117 card payments - four fewer card payments than the query finds. The query side is self-consistent across all three groupings, so the disagreement is between the two views, not within the query. Reproduced on both repeats. The case names four gateways; only BillPay can run it. SnapPay's query table holds card activity only (Category is CardSale throughout) so the precondition of a range with both card and ACH activity is not met. MerchantE's query panel is inert (PS-PQ-16). NuveiPay has no query panel (PS-PQ-01).</t>
+          <t xml:space="preserve">QA 2026-09-21, RE-CONFIRMED BY HAND 2026-09-24. Automated on BillPay as two tests. PASS - regrouping re-splits the same payments, and a Having clause of funding_method!='ACH' narrows the table while leaving the graph untouched. DEFECT (expected-fail test) - the graph and the query table disagree about the same payments over the same range. Manual re-check on 2026-09-24 over 90 days (06/26-09/24), Select and Group reduced to Funding Method alone so the counts could be read straight off: ACH 95, DISCOVER 21, MASTERCARD 45, PULSE 2, VISA 49 - so 95 ACH against 117 card, 212 in total, a 44.81% ACH share. The graph drew 45.45%. Working back, 95/0.4545 = 209 total, so the graph counts only 114 card payments - three fewer than the table. LEAD ON THE CAUSE (not proven): the gap is exactly three, and the detailed breakdown holds one MASTERCARD AppleSale payment and two PULSE payments, which is exactly three. That points at the graph deciding what counts as a card from a fixed list of brands or categories and dropping anything outside it, while the table counts everything that is not ACH. Needs checking before it is believed. RANGE MATTERS: over the default 30-day range the two views agree exactly (40 ACH, 46 card, graph 46.51/53.49). Anyone reproducing this on the default range will conclude there is no defect. Use 90 days, or any range containing an AppleSale or PULSE payment. The query side is self-consistent across all three groupings, so the disagreement is between the two views, not within the query. The case names four gateways; only BillPay can run it - MerchantE's panel is inert (PS-PQ-16) and NuveiPay has no panel (PS-PQ-01). Written up as defect 8 in PaymentStats_Bugs.docx with the arithmetic marked on the screenshots.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -2158,7 +2158,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-17 IPG, DEFECT CONFIRMED with source evidence, expected result rewritten. Submit reported enabled in every state a merchant can actually reach: on load, and with From Date cleared entirely - the disabled attribute was absent throughout. (An inverted range was also tried, but only by typing a date past the picker's minimum; the To Date calendar greys out every day before the current From Date, so that state cannot be produced from the UI and is not part of this case.) The cause is not missing logic: isSubmitButtonDisabled is declared at index.js:86 and updated in five places, but the line that applies it is commented out at index.js:606 - // disabled={isSubmitButtonDisabled}. Uncommenting it is the whole fix.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG, DEFECT CONFIRMED with source evidence, expected result rewritten. Submit reported enabled in every state a merchant can actually reach: on load, and with From Date cleared entirely - the disabled attribute was absent throughout. (An inverted range was also tried, but only by typing a date past the picker's minimum; the To Date calendar greys out every day before the current From Date, so that state cannot be produced from the UI and is not part of this case.) The cause is not missing logic: isSubmitButtonDisabled is declared at index.js:86 and updated in five places, but the line that applies it is commented out at index.js:606 - // disabled={isSubmitButtonDisabled}. Uncommenting it is the whole fix. RE-CONFIRMED 2026-09-24 on IPG, and the finding goes further than first recorded. Submit is not only enabled - it accepts the click and the query runs. With From Date cleared entirely, pressing Submit returned a full result: Card Payments $44,903.20 across 708 payments, while the From Date box stayed empty. No message appeared and nothing on the page states what period those figures cover. That second half is the reason this matters: an enabled button that does nothing is an annoyance, but one that returns figures for an unstated period is something a merchant reads as an answer. Written up as defect 10 in PaymentStats_Bugs.docx with three marked screenshots.</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-17 IPG, DEFECT CONFIRMED. Every payment_stats_us call carried clientRequestId=1647602068707, the same fixed value on page load and after a date change, exactly as apis/payment.js:101 hard-codes it. Two requests cannot be told apart in logs or traced individually. This is one of only three places in the module where the test reads the network, because the parameter has no UI surface of any kind.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG, DEFECT CONFIRMED. Every payment_stats_us call carried clientRequestId=1647602068707, the same fixed value on page load and after a date change, exactly as apis/payment.js:101 hard-codes it. Two requests cannot be told apart in logs or traced individually. This is one of only three places in the module where the test reads the network, because the parameter has no UI surface of any kind. RE-CONFIRMED 2026-09-24 on BillPay - the same value 1647602068707, on a different merchant a week later, and on two requests within one session (a 30-day range and a 90-day range) that differed in every other respect. So the value is fixed in the source, not per-session or per-merchant. WHAT THE VALUE TELLS YOU: read as a millisecond timestamp, 1647602068707 is 18 March 2022 11:14:28 UTC - a Date.now() result from one development session pasted in as a constant instead of left as a call. The intent was right; only the call was replaced by its result. Worth checking whether the same literal was pasted elsewhere at the same time, and whether anything downstream has come to rely on it being fixed after four and a half years. Written up as defect 11 in PaymentStats_Bugs.docx, with no screenshots because the parameter has no UI surface.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -6012,7 +6012,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-24 DEFECT CONFIRMED. Verified twice and they agree: automated (connection cut in Playwright) and manually in the browser with DevTools &gt; Network &gt; Offline, with before/after screenshots. USER-VISIBLE HARM (the main point): after Submit fails, the table keeps showing the PREVIOUS results unchanged and no message appears anywhere on screen. Confirmed by comparing the two screenshots - From Date changed from 08/25/2026 to 07/24/2026, Submit pressed, request failed, and the same rows (ACH/CheckSale, DISCOVER/CreditSale, MASTERCARD/CreditSale...) are still listed. The merchant is left believing those figures answer the new date range. The only way to find out is to open DevTools. CONSOLE: the failure handler then breaks three times over: 'err: TypeError: Cannot convert undefined or null to object' (Object.keys on undefined), 'err: TypeError: Cannot read properties of undefined (reading error_code)', and 'Uncaught (in promise) ReferenceError: err is not defined'. It reaches into a response object that does not exist, because the request never completed. NOTE FOR ANYONE REPRODUCING: the first two are logged at info/log level, not error, so they carry no red icon and are invisible if the console filter is set to Errors only. The real cause is NOT lost - the browser logs net::ERR_INTERNET_DISCONNECTED itself, two lines above. Each of the three is asserted separately so a partial fix shows as progress.</t>
+          <t xml:space="preserve">QA 2026-09-24 DEFECT CONFIRMED. Verified twice and they agree: automated (connection cut in Playwright) and manually in the browser with DevTools &gt; Network &gt; Offline, with before/after screenshots. USER-VISIBLE HARM (the main point): after Submit fails, the table keeps showing the PREVIOUS results unchanged and no message appears anywhere on screen. Confirmed by comparing the two screenshots - From Date changed from 08/25/2026 to 07/24/2026, Submit pressed, request failed, and the same rows (ACH/CheckSale, DISCOVER/CreditSale, MASTERCARD/CreditSale...) are still listed. The merchant is left believing those figures answer the new date range. The only way to find out is to open DevTools. CONSOLE: the failure handler then breaks three times over: 'err: TypeError: Cannot convert undefined or null to object' (Object.keys on undefined), 'err: TypeError: Cannot read properties of undefined (reading error_code)', and 'Uncaught (in promise) ReferenceError: err is not defined'. It reaches into a response object that does not exist, because the request never completed. NOTE FOR ANYONE REPRODUCING: the first two are logged at info/log level, not error, so they carry no red icon and are invisible if the console filter is set to Errors only. The real cause is NOT lost - the browser logs net::ERR_INTERNET_DISCONNECTED itself, two lines above. Each of the three is asserted separately so a partial fix shows as progress. PRIORITY RAISED Medium -&gt; High on 2026-09-24, to match the write-up. The harm is the same shape as PS-LOAD-10, which is already High: the merchant is shown wrong figures with nothing saying so. Three things decided it - there is no signal at all, so the merchant cannot self-correct; the wrongness is total rather than a small gap, since every figure answers a different question from the one asked; and the trigger is ordinary, a dropped connection or a VPN reconnect. Not raised to Critical because it needs a network failure first, whereas PS-NEG-11 needs only a refresh and PS-NEG-12 needs only the calendar to reach October.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -4117,7 +4117,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 BillPay: removing every Select chip left 0 chips and the Execute button became disabled.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: removing every Select chip left 0 chips and the Execute button became disabled. WHY THIS SAYS Automated AND NOT Automated (expected fail), noted 2026-09-24 because the two look contradictory side by side: the test asserts what the panel does TODAY, not what it ought to do, so it passes. Emptying Select and then putting a field back frees up Group, but Having and Execute stay locked until Group itself is touched. The test records that partial recovery deliberately, so it is not mistaken for a flake. It will start FAILING the day the recovery is fixed, and that failure is the signal to flip the expectation - the failure message says so. The defect itself is written up as defect 3 in PaymentStats_Bugs.docx.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -6225,13 +6225,13 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blocked</t>
+          <t xml:space="preserve">Not Automated</t>
         </is>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blocked</t>
+          <t xml:space="preserve">Not verified</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-21 BLOCKED - the Transactions grid's Date &amp; Time column filter does not filter. Measured on sub-merchant 44052730 (29,069 transactions), driving the popover directly: the date box wants YYYY-MM-DD rather than the MM/DD/YYYY the grid displays; typing 2026-09-19 lands correctly and Search does enable; but 'is equal to', 'greater than or equal to' and 'less than or equal to' each returned the full 29,069 rows, still showing 9/21 dates the filter should have excluded. Without a working date filter the comparison is a single day on one page against every transaction ever on the other, which proves nothing. SEPARATELY WORTH RAISING: Payment Stats defaults to sub-merchant 44052731 and reports card payments under it, while All Transactions lists nothing at all for that same sub-merchant; any reconciliation must pin both pages to 44052730.</t>
+          <t xml:space="preserve">QA 2026-09-24 NO LONGER BLOCKED - the Transactions Date and Time filter works. The 2026-09-21 note below it is out of date. Verified by hand on WGL over both pages: on Payments, between 2019-01-01 and 2019-12-31 returned 0 of 0 while between 2026-06-23 and 2026-09-24 returned 542; on All Transactions the same two ranges returned 0 and 903 against a 4,511 baseline. The 'between' condition did not exist on 2026-09-21 and does now, so a fix appears to have landed alongside it. RECONCILE ON THE PAYMENTS PAGE, not All Transactions: Payment Stats counts payments, while All Transactions also carries refunds and voids. Both filter correctly, so this is a choice about what is being compared rather than about which one works. STILL PIN THE SUB-MERCHANT. Payment Stats defaults to 44052731 and reports card payments under it while All Transactions lists nothing at all for that sub-merchant, so both pages must be set to 44052730 before any comparison. That half of the original note still stands. NOT YET AUTOMATED, and the reason is worth knowing before anyone tries. The Payment Stats half is straightforward. The Transactions half could not be driven from Playwright on 2026-09-24: six approaches were tried - fill(), typed with Tab, typed with Enter, the native value setter with input and change events, the calendar picker with both dates set, and a geometry-matched filter icon - and in every case the dates appeared in the input boxes while the request still carried only paymentEventID. The date never reached the application's state. Reading the input value back does NOT prove the filter registered; capture the outgoing request instead. CORRECTION FOR THE RECORD: an automated attempt that same day reported the filter returning every row on both pages. That was the automation failing to deliver the dates, not the product. ALSO: FilterTable.countDateInputs() returns 0 for these fields, so any helper built on it silently skips the input - locate them by their YYYY-MM-DD placeholder. TC-DT-FILTER-N01 and N02 in filter-datetime-all-conditions.spec.ts are currently failing for this same automation reason rather than for an application fault. PREVIOUS NOTE, 2026-09-21, now superseded: QA 2026-09-21 BLOCKED - the Transactions grid's Date &amp; Time column filter does not filter. Measured on sub-merchant 44052730 (29,069 transactions), driving the popover directly: the date box wants YYYY-MM-DD rather than the MM/DD/YYYY the grid displays; typing 2026-09-19 lands correctly and Search does enable; but 'is equal to', 'greater than or equal to' and 'less than or equal to' each returned the full 29,069 rows, still showing 9/21 dates the filter should have excluded. Without a working date filter the comparison is a single day on one page against every transaction ever on the other, which proves nothing. SEPARATELY WORTH RAISING: Payment Stats defaults to sub-merchant 44052731 and reports card payments under it, while All Transactions lists nothing at all for that same sub-merchant; any reconciliation must pin both pages to 44052730.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -7752,7 +7752,7 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: CORRECTED - the dashboard fires its own periodic call (pageSize=12) before you reach Trends. Count only the request made by the Trends page itself.</t>
+          <t xml:space="preserve">QA 2026-09-14: CORRECTED - the dashboard fires its own periodic call (pageSize=12) before you reach Trends. Count only the request made by the Trends page itself. NARROWED 2026-09-25. The test now reads only pageNumber off the request, plus the 200. pageDefination and pageSize are no longer re-checked here because both have a visible consequence that is already asserted on screen: pageSize=6 gives six month labels and pageDefination=monthly gives labels reading 'Apr 2026' rather than days or weeks, both covered by PT-LOAD-06, and the range control reading 'Last 6 Months' is covered by PT-LOAD-04. Checking them again on the wire duplicated that cover. pageNumber stays because it is the only one of the four with no consequence a merchant could see - there is no paging control on the chart. sub_merchant_id also stays, and is now compared against the sub-merchant shown on screen rather than merely checked for being non-blank. WORTH BEING CLEAR ABOUT WHAT THIS CASE DOES: nothing here calls the API. The page is opened through the sidebar the way a merchant would and the test listens to the request the page itself sends, which is what step 5 means by inspecting it in DevTools. A test that called the endpoint directly would pass with the page completely broken.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -7926,7 +7926,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automated</t>
+          <t xml:space="preserve">Automated (expected fail)</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified</t>
+          <t xml:space="preserve">Corrected after run</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14 MerchantE/CommerceHub/NuveiPaya all rendered empty charts with axes and month labels intact, no console error.</t>
+          <t xml:space="preserve">QA 2026-09-14 MerchantE/CommerceHub/NuveiPaya all rendered empty charts with axes and month labels intact, no console error. QA 2026-09-24 DEFECT FOUND, and it CONTRADICTS the note above - read both. A merchant whose stats call succeeds with no payments draws NO month labels at all: the heading, the value axis and both captions render and the x-axis is blank. Measured on merchantE, which returns 200 with every monthly count zero and zero labels. A merchant whose call FAILS draws six labels normally, so the error path falls back to a properly labelled empty chart while the success-with-no-data path does not. Either the behaviour changed since 2026-09-14 or the earlier observation was taken on an account that was erroring rather than empty - which is exactly what the test was doing. WHY IT WAS NEVER CAUGHT: the test ran on nuveiPayaConnect, whose call returns 400/404, so it passed against an error state for weeks; a recorded run shows the page carrying a red 'Request failed with status code 404' toast while the test went green. Moved to merchantE and guarded so it cannot drift back: it now asserts the response is 200, that the returned counts sum to zero, and that no error toast appeared. Marked test.fail() until the labels come back, hence the status change. Needs a write-up in the Payment Trends defects document, not PaymentStats_Bugs.docx.</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N79" s="2"/>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14 SnapPay: left axis ticks read 0,5,10...60 as bare numbers - no ' k' suffix. Confirmed defect.</t>
+          <t xml:space="preserve">QA 2026-09-14 SnapPay: left axis ticks read 0,5,10...60 as bare numbers - no ' k' suffix. Confirmed defect. QA 2026-09-25 STATUS CORRECTED to Automated - a test has existed for this since 2026-09-24 and the row still read Not Automated. It covers the LEFT AXIS ONLY. The right-hand axis the case also asks about never renders at all (PT-LOAD-10), so it has no ticks to judge; the test reads whatever axes do paint, so if it is ever wired up its ticks are held to the same rule without further change. The axes are found by SHAPE rather than by content, deliberately: matching on 'looks like a number' would skip the very labels this case is about, since a tick drawn as '20 k' has to be found before it can be judged. Listed as plain Automated rather than expected-fail because, like PS-PQ-05, the test asserts what the panel does today rather than what it ought to do, so it passes now and will start failing the day the suffixes are applied - and its failure message says so. Needs a write-up in the Payment Trends defects document.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -7957,7 +7957,7 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14 MerchantE/CommerceHub/NuveiPaya all rendered empty charts with axes and month labels intact, no console error. QA 2026-09-24 DEFECT FOUND, and it CONTRADICTS the note above - read both. A merchant whose stats call succeeds with no payments draws NO month labels at all: the heading, the value axis and both captions render and the x-axis is blank. Measured on merchantE, which returns 200 with every monthly count zero and zero labels. A merchant whose call FAILS draws six labels normally, so the error path falls back to a properly labelled empty chart while the success-with-no-data path does not. Either the behaviour changed since 2026-09-14 or the earlier observation was taken on an account that was erroring rather than empty - which is exactly what the test was doing. WHY IT WAS NEVER CAUGHT: the test ran on nuveiPayaConnect, whose call returns 400/404, so it passed against an error state for weeks; a recorded run shows the page carrying a red 'Request failed with status code 404' toast while the test went green. Moved to merchantE and guarded so it cannot drift back: it now asserts the response is 200, that the returned counts sum to zero, and that no error toast appeared. Marked test.fail() until the labels come back, hence the status change. Needs a write-up in the Payment Trends defects document, not PaymentStats_Bugs.docx.</t>
+          <t xml:space="preserve">QA 2026-09-14 MerchantE/CommerceHub/NuveiPaya all rendered empty charts with axes and month labels intact, no console error. QA 2026-09-24 DEFECT FOUND, and it CONTRADICTS the note above - read both. A merchant whose stats call succeeds with no payments draws NO month labels at all: the heading, the value axis and both captions render and the x-axis is blank. Measured on merchantE, which returns 200 with every monthly count zero and zero labels. A merchant whose call FAILS draws six labels normally, so the error path falls back to a properly labelled empty chart while the success-with-no-data path does not. Either the behaviour changed since 2026-09-14 or the earlier observation was taken on an account that was erroring rather than empty - which is exactly what the test was doing. WHY IT WAS NEVER CAUGHT: the test ran on nuveiPayaConnect, whose call returns 400/404, so it passed against an error state for weeks; a recorded run shows the page carrying a red 'Request failed with status code 404' toast while the test went green. Moved to merchantE and guarded so it cannot drift back: it now asserts the response is 200, that the returned counts sum to zero, and that no error toast appeared. Marked test.fail() until the labels come back, hence the status change. Needs a write-up in the Payment Trends defects document, not PaymentStats_Bugs.docx. CORRECTION 2026-09-25: 'empty merchant' is too narrow and the description above is wrong on that point. CommerceHub has 35 payments in the range and ALSO draws no month names. Measured across all six accounts: IPG 2,436 payments / 6 names, WGL 2,090 / 6, SnapPay 224 / 6, CommerceHub 35 / NONE, MerchantE 0 / NONE, NuveiPaya call failed / 6. What the two broken ones share is a SHORT RESPONSE rather than an empty one - they returned 2 and 3 monthly figures where the three working accounts returned 12. So the trigger appears to be a response covering fewer months than were asked for, not an absence of payments. Confirmed as a bug either way; the cause needs re-checking on CommerceHub before the write-up is drafted.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -8539,7 +8539,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N83" s="2"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 SnapPay: selecting Last 24 Months redrew the chart with exactly 24 month labels spanning two years.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: selecting Last 24 Months redrew the chart with exactly 24 month labels spanning two years. AUTOMATED 2026-09-25. Only what was not already covered is asserted; the PT-RANGE-01/02/03 test already walks 3, 12 and 24 months and checks their label counts, the newest label and rotation. The case says a 24-month window spans two calendar years. That is only true in December - ending in September it covers 2024, 2025 and 2026. The test builds the expected years from the clock rather than counting to two, so the case wording is the imprecise part.</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N84" s="2"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14 SnapPay: drill-down was open, switching to Last 12 Months removed it.</t>
+          <t xml:space="preserve">QA 2026-09-14 SnapPay: drill-down was open, switching to Last 12 Months removed it. AUTOMATED 2026-09-25. Only what was not already covered is asserted; the PT-RANGE-01/02/03 test already walks 3, 12 and 24 months and checks their label counts, the newest label and rotation. First test in the suite to open the month drill-down. Worth more than the case itself: PT-LOAD-08 asserts the same four elements are ABSENT on load, and nothing had ever proved those selectors match when the panel IS open, so it could have passed with all four wrong.</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N85" s="2"/>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14 SnapPay: 6 months rendered 0 rotated labels, 12 months rendered 12. Boundary holds.</t>
+          <t xml:space="preserve">QA 2026-09-14 SnapPay: 6 months rendered 0 rotated labels, 12 months rendered 12. Boundary holds. AUTOMATED 2026-09-25. Only what was not already covered is asserted; the PT-RANGE-01/02/03 test already walks 3, 12 and 24 months and checks their label counts, the newest label and rotation. Pins the rotation boundary at six. The sibling test proves zero rotation at THREE, which would still pass if the condition were written as &gt;= 6 instead of &gt; 6. Also checks the return leg, 12 back down to 6.</t>
         </is>
       </c>
     </row>
@@ -8836,13 +8836,13 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Verified</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -8860,7 +8860,11 @@
           <t xml:space="preserve">PaymentTrends/index.js:893-901,585-590</t>
         </is>
       </c>
-      <c r="S86" s="2"/>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> AUTOMATED 2026-09-25. Only what was not already covered is asserted; the PT-RANGE-01/02/03 test already walks 3, 12 and 24 months and checks their label counts, the newest label and rotation. Selects all four ranges in order, including Last 6 Months, which the sibling test never picks because six is where the page starts.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2">
@@ -8973,7 +8977,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT-LEG-04</t>
+          <t xml:space="preserve">PT-LEG-02</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -9068,7 +9072,7 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14: CONFIRMED on SnapPay and CommerceHub - both rendered ['Token','Card']. MerchantE could NOT be confirmed: its periodic call returned 400 so the gateway never resolved and the legend fell back to ['Ach','Card'] - see PT-NEG-11. Re-test MerchantE once the QA data is fixed.</t>
+          <t xml:space="preserve">QA 2026-09-14: CONFIRMED on SnapPay and CommerceHub - both rendered ['Token','Card']. MerchantE could NOT be confirmed: its periodic call returned 400 so the gateway never resolved and the legend fell back to ['Ach','Card'] - see PT-NEG-11. Re-test MerchantE once the QA data is fixed. RENUMBERED 2026-09-25 from PT-LEG-04, so the block runs without gaps.</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9082,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT-LEG-07</t>
+          <t xml:space="preserve">PT-LEG-03</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -9165,7 +9169,7 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 Paymentus: legend read ['Ach','Token','Card'] - the only gateway showing all three series.</t>
+          <t xml:space="preserve">QA 2026-09-15 Paymentus: legend read ['Ach','Token','Card'] - the only gateway showing all three series. RENUMBERED 2026-09-25 from PT-LEG-07, so the block runs without gaps.</t>
         </is>
       </c>
     </row>
@@ -9175,7 +9179,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT-LEG-08</t>
+          <t xml:space="preserve">PT-LEG-04</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -9265,7 +9269,7 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">India account not included in this token refresh.</t>
+          <t xml:space="preserve">India account not included in this token refresh. RENUMBERED 2026-09-25 from PT-LEG-08, so the block runs without gaps.</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9341,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N91" s="2"/>
@@ -9363,7 +9367,7 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14 IPG: hovering the tallest bar produced Ach(0) and Card(544) - ACH and Card only, no Token line.</t>
+          <t xml:space="preserve">QA 2026-09-14 IPG: hovering the tallest bar produced Ach(0) and Card(544) - ACH and Card only, no Token line. AUTOMATED 2026-09-25. Only what was not already covered is asserted; the PT-RANGE-01/02/03 test already walks 3, 12 and 24 months and checks their label counts, the newest label and rotation. Series names are read from the tooltip text, never the legend - the legend selector also matches tooltip lines while hovering, so reading it mid-hover would be reading the thing under test.</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11051,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT-CARD-05</t>
+          <t xml:space="preserve">PT-CARD-04</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -11134,7 +11138,7 @@
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">India account not included in this token refresh.</t>
+          <t xml:space="preserve">India account not included in this token refresh. RENUMBERED 2026-09-25 from PT-CARD-05, so the block runs without gaps.</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11148,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT-CARD-06</t>
+          <t xml:space="preserve">PT-CARD-05</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -11232,7 +11236,7 @@
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 Paymentus: card counts matched the tooltip exactly for the same month (29 / 246 / 63). Note the drill-down table holds 198 rows because it is filtered to Sale requests, so it is not expected to equal the sum of the cards.</t>
+          <t xml:space="preserve">QA 2026-09-15 Paymentus: card counts matched the tooltip exactly for the same month (29 / 246 / 63). Note the drill-down table holds 198 rows because it is filtered to Sale requests, so it is not expected to equal the sum of the cards. RENUMBERED 2026-09-25 from PT-CARD-06, so the block runs without gaps.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -9143,7 +9143,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N89" s="2"/>
@@ -9169,7 +9169,7 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 Paymentus: legend read ['Ach','Token','Card'] - the only gateway showing all three series. RENUMBERED 2026-09-25 from PT-LEG-07, so the block runs without gaps.</t>
+          <t xml:space="preserve">QA 2026-09-15 Paymentus: legend read ['Ach','Token','Card'] - the only gateway showing all three series. RENUMBERED 2026-09-25 from PT-LEG-07, so the block runs without gaps. AUTOMATED 2026-09-25 on the Paymentus account, which was in credentials as active but missing from the token pool until it was regenerated. Asserts the legend is exactly ['Ach','Token','Card'] - Paymentus is the only gateway drawing all three, so this is what stops PT-LEG-01 and PT-LEG-02's exact two-entry arrays being read as 'a legend may only ever have two series'. The legend is read with nothing hovered, because its selector also matches tooltip lines.</t>
         </is>
       </c>
     </row>
@@ -9243,13 +9243,13 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Blocked</t>
         </is>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Blocked - no India account</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">India account not included in this token refresh. RENUMBERED 2026-09-25 from PT-LEG-08, so the block runs without gaps.</t>
+          <t xml:space="preserve">India account not included in this token refresh. RENUMBERED 2026-09-25 from PT-LEG-08, so the block runs without gaps. BLOCKED 2026-09-25 - no India merchant account. The india and indiaAdmin entries in credentials/qa.json are both active:false, so no token is generated and nothing can run against an India merchant. Confirmed with the user on 2026-09-25 that India is not being tested, so this is not pending work. Re-open only if an India account is activated.</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N93" s="2"/>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 Paymentus: tooltip showed Ach(29), Token(246) and Card(63) together.</t>
+          <t xml:space="preserve">QA 2026-09-15 Paymentus: tooltip showed Ach(29), Token(246) and Card(63) together. AUTOMATED 2026-09-25 on Paymentus. Asserts the tooltip carries exactly Ach, Token and Card, and that each count reads as a whole number rather than merely matching a text pattern. Measured on the day: Ach 29, Token 246, Card 63.</t>
         </is>
       </c>
     </row>
@@ -10317,13 +10317,13 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Blocked</t>
         </is>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Blocked - no India account</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">India account not included in this token refresh.</t>
+          <t xml:space="preserve">India account not included in this token refresh. BLOCKED 2026-09-25 - no India merchant account, same as PT-LEG-04. The india and indiaAdmin entries in credentials/qa.json are both active:false, so no token is generated and nothing can run against an India merchant. Confirmed with the user that India is not being tested, so this is not pending work. Re-open only if an India account is activated.</t>
         </is>
       </c>
     </row>
@@ -11112,13 +11112,13 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Blocked</t>
         </is>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Blocked - no India account</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">India account not included in this token refresh. RENUMBERED 2026-09-25 from PT-CARD-05, so the block runs without gaps.</t>
+          <t xml:space="preserve">India account not included in this token refresh. RENUMBERED 2026-09-25 from PT-CARD-05, so the block runs without gaps. BLOCKED 2026-09-25 - no India merchant account, same as PT-LEG-04. The india and indiaAdmin entries in credentials/qa.json are both active:false, so no token is generated and nothing can run against an India merchant. Confirmed with the user that India is not being tested, so this is not pending work. Re-open only if an India account is activated.</t>
         </is>
       </c>
     </row>
@@ -11405,13 +11405,13 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Blocked</t>
         </is>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Blocked - no India account</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">India account not included in this token refresh.</t>
+          <t xml:space="preserve">India account not included in this token refresh. BLOCKED 2026-09-25 - no India merchant account, same as PT-LEG-04. The india and indiaAdmin entries in credentials/qa.json are both active:false, so no token is generated and nothing can run against an India merchant. Confirmed with the user that India is not being tested, so this is not pending work. Re-open only if an India account is activated.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -9628,7 +9628,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N94" s="2"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 SnapPay: tooltip read Token(3) and Card(52); the summary cards for the same month read Token (3) and Card (52) - identical.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: tooltip read Token(3) and Card(52); the summary cards for the same month read Token (3) and Card (52) - identical. AUTOMATED 2026-09-25 on wglUsa, snapPay and paymentus. Measured first rather than reasoned about, by hovering and clicking the SAME bar: wglUsa Ach 43 / Card 80, snapPay Token 19 / Card 92, paymentus Ach 29 / Token 246 / Card 63 - tooltip and cards identical on all three. IPG IS DELIBERATELY EXCLUDED. There the tooltip read Ach 0 / Card 712 while the cards read Ach 0 / Card 0. That mismatch is a real defect but it is already logged twice, as PT-NEG-12 and PT-NEG-13, so running this case on IPG would fail correctly while only re-reporting those. CORRECTION to an earlier analysis: it was claimed the two numbers come from different sources and could legitimately differ, which would have made this case unsound. They agree on three of four gateways, so the case is sound and the earlier reading was wrong. Note for anyone extending it: hoverNewestMonthColumn() takes the newest bar and clickTallestBar() the tallest, so using them together compares two different months. hoverTallestBar() and pressAtPointer() were added to work on one bar.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -6225,13 +6225,13 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Automated</t>
+          <t xml:space="preserve">Automated (partial)</t>
         </is>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">Stats side verified; Transactions side manual</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-24 NO LONGER BLOCKED - the Transactions Date and Time filter works. The 2026-09-21 note below it is out of date. Verified by hand on WGL over both pages: on Payments, between 2019-01-01 and 2019-12-31 returned 0 of 0 while between 2026-06-23 and 2026-09-24 returned 542; on All Transactions the same two ranges returned 0 and 903 against a 4,511 baseline. The 'between' condition did not exist on 2026-09-21 and does now, so a fix appears to have landed alongside it. RECONCILE ON THE PAYMENTS PAGE, not All Transactions: Payment Stats counts payments, while All Transactions also carries refunds and voids. Both filter correctly, so this is a choice about what is being compared rather than about which one works. STILL PIN THE SUB-MERCHANT. Payment Stats defaults to 44052731 and reports card payments under it while All Transactions lists nothing at all for that sub-merchant, so both pages must be set to 44052730 before any comparison. That half of the original note still stands. NOT YET AUTOMATED, and the reason is worth knowing before anyone tries. The Payment Stats half is straightforward. The Transactions half could not be driven from Playwright on 2026-09-24: six approaches were tried - fill(), typed with Tab, typed with Enter, the native value setter with input and change events, the calendar picker with both dates set, and a geometry-matched filter icon - and in every case the dates appeared in the input boxes while the request still carried only paymentEventID. The date never reached the application's state. Reading the input value back does NOT prove the filter registered; capture the outgoing request instead. CORRECTION FOR THE RECORD: an automated attempt that same day reported the filter returning every row on both pages. That was the automation failing to deliver the dates, not the product. ALSO: FilterTable.countDateInputs() returns 0 for these fields, so any helper built on it silently skips the input - locate them by their YYYY-MM-DD placeholder. TC-DT-FILTER-N01 and N02 in filter-datetime-all-conditions.spec.ts are currently failing for this same automation reason rather than for an application fault. PREVIOUS NOTE, 2026-09-21, now superseded: QA 2026-09-21 BLOCKED - the Transactions grid's Date &amp; Time column filter does not filter. Measured on sub-merchant 44052730 (29,069 transactions), driving the popover directly: the date box wants YYYY-MM-DD rather than the MM/DD/YYYY the grid displays; typing 2026-09-19 lands correctly and Search does enable; but 'is equal to', 'greater than or equal to' and 'less than or equal to' each returned the full 29,069 rows, still showing 9/21 dates the filter should have excluded. Without a working date filter the comparison is a single day on one page against every transaction ever on the other, which proves nothing. SEPARATELY WORTH RAISING: Payment Stats defaults to sub-merchant 44052731 and reports card payments under it, while All Transactions lists nothing at all for that same sub-merchant; any reconciliation must pin both pages to 44052730.</t>
+          <t xml:space="preserve">QA 2026-09-24 NO LONGER BLOCKED - the Transactions Date and Time filter works. The 2026-09-21 note below it is out of date. Verified by hand on WGL over both pages: on Payments, between 2019-01-01 and 2019-12-31 returned 0 of 0 while between 2026-06-23 and 2026-09-24 returned 542; on All Transactions the same two ranges returned 0 and 903 against a 4,511 baseline. The 'between' condition did not exist on 2026-09-21 and does now, so a fix appears to have landed alongside it. RECONCILE ON THE PAYMENTS PAGE, not All Transactions: Payment Stats counts payments, while All Transactions also carries refunds and voids. Both filter correctly, so this is a choice about what is being compared rather than about which one works. STILL PIN THE SUB-MERCHANT. Payment Stats defaults to 44052731 and reports card payments under it while All Transactions lists nothing at all for that sub-merchant, so both pages must be set to 44052730 before any comparison. That half of the original note still stands. NOT YET AUTOMATED, and the reason is worth knowing before anyone tries. The Payment Stats half is straightforward. The Transactions half could not be driven from Playwright on 2026-09-24: six approaches were tried - fill(), typed with Tab, typed with Enter, the native value setter with input and change events, the calendar picker with both dates set, and a geometry-matched filter icon - and in every case the dates appeared in the input boxes while the request still carried only paymentEventID. The date never reached the application's state. Reading the input value back does NOT prove the filter registered; capture the outgoing request instead. CORRECTION FOR THE RECORD: an automated attempt that same day reported the filter returning every row on both pages. That was the automation failing to deliver the dates, not the product. ALSO: FilterTable.countDateInputs() returns 0 for these fields, so any helper built on it silently skips the input - locate them by their YYYY-MM-DD placeholder. TC-DT-FILTER-N01 and N02 in filter-datetime-all-conditions.spec.ts are currently failing for this same automation reason rather than for an application fault. PREVIOUS NOTE, 2026-09-21, now superseded: QA 2026-09-21 BLOCKED - the Transactions grid's Date &amp; Time column filter does not filter. Measured on sub-merchant 44052730 (29,069 transactions), driving the popover directly: the date box wants YYYY-MM-DD rather than the MM/DD/YYYY the grid displays; typing 2026-09-19 lands correctly and Search does enable; but 'is equal to', 'greater than or equal to' and 'less than or equal to' each returned the full 29,069 rows, still showing 9/21 dates the filter should have excluded. Without a working date filter the comparison is a single day on one page against every transaction ever on the other, which proves nothing. SEPARATELY WORTH RAISING: Payment Stats defaults to sub-merchant 44052731 and reports card payments under it, while All Transactions lists nothing at all for that same sub-merchant; any reconciliation must pin both pages to 44052730. HALF AUTOMATED 2026-09-25 - the Payment Stats side only. The Transactions side stays MANUAL and the test says so. It sets a fixed, repeatable window (the last complete calendar month) on wglUsa, sums the funding-method rows into an ACH total and a card total, checks every row carries a method and a whole-number count, and attaches the figures, the window, the per-method breakdown and the manual steps to the run so whoever finishes it has everything without re-deriving it. WHY IT IS SPLIT: the Transactions Date and Time filter WORKS - proved by hand, 2019 returned 0 of 0 and the last three months returned 542 against a 4,511 baseline. What could not be done is driving it from a test. It is a MUI X v6 DatePicker with a segmented field, and six approaches all left the date visible in the box while the request carried no filter: fill(), typed with Tab, typed with Enter, the native value setter with input and change events, typing digits into the segments, and picking from the calendar. The product is fine; the automation is not. NOTE ON THE GATEWAY: wglUsa, not ipg. IPG draws the Card Payments / ACH Payments summary directly, which would be simpler to read, but its Transactions side returns nothing (PT-NEG-12) so the manual half would have had nothing to compare against. BillPay draws the funding-method breakdown instead, hence the summing. STILL PIN THE SUB-MERCHANT before comparing: Payment Stats defaults to 44052731 while All Transactions lists nothing for it, so set both pages to 44052730. And reconcile on PAYMENTS, not All Transactions, which also carries refunds and voids.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -15388,82 +15388,6 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2">
-        <v>152</v>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PS-OBS-01</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Payment Stats</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S9. Incidental Observations</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A config call fails with 400 on page load because merchantId is sent as undefined</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Customer-portal user signed in through the UI (not token injection); DevTools open on the Network and Console tabs from before the first request</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No fault injected. A completely healthy session.
-Gateway seen on: IPG</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open DevTools and select the Console tab, with the level filter left on Default levels
-2. Sign in to the customer portal through the sign-in form
-3. Open Payment Stats from Payment Analytics
-4. Read the console without applying any filter
-5. Switch to the Network tab and look for calls to /v1/merchant/ui_config
-6. Check the merchantId value in the query string of the first such call</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Every request on a healthy page load carries a real merchant id and returns 2xx. No 400 appears in the console when nothing has gone wrong.</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="M153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Automated</t>
-        </is>
-      </c>
-      <c r="O153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed, not confirmed</t>
-        </is>
-      </c>
-      <c r="Q153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IPG (seen); other gateways unchecked</t>
-        </is>
-      </c>
-      <c r="S153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">QA 2026-09-24 OBSERVED, NOT YET CONFIRMED AS A DEFECT - deliberately not called a bug yet. Spotted in a merchant&amp;#8217;s own DevTools console while reproducing PS-NEG-02, on a healthy page with nothing injected: "Failed to load resource: the server responded with a status of 400" against qaapi1.tillipay.com, with merchantId=undefined in the query string. WHAT IS PROVEN: the endpoint is GET /v1/merchant/ui_config?merchantId=&lt;id&gt;, and on a normal load it is called five times over, which is worth a look on its own. WHAT IS NOT PROVEN: the cause. It does NOT reproduce in automation - on repeated IPG runs the parameter always carried a real value (526971115880) and not one request failed. The difference is that the automation writes mainMerchantId into localStorage before the app starts, so the value is ready earlier than it would be after a real sign-in. That points at a start-up ordering problem, where the first ui_config call goes out before the merchant id has been set - but that is a hypothesis, not a measurement, and it should not be written up as a defect until someone has watched it happen. TO CONFIRM: sign in through the form rather than by injecting a token, watch the Network tab from the very first request, and see whether the first ui_config call carries undefined. IMPACT IF REAL: one failed config call on every fresh sign-in, and whatever ui_config drives is left to fall back on defaults. Not blocking - the page still loads and the figures are correct.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:S1"/>
 </worksheet>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -4086,7 +4086,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automated</t>
+          <t xml:space="preserve">Automated (expected fail)</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 BillPay: removing every Select chip left 0 chips and the Execute button became disabled. WHY THIS SAYS Automated AND NOT Automated (expected fail), noted 2026-09-24 because the two look contradictory side by side: the test asserts what the panel does TODAY, not what it ought to do, so it passes. Emptying Select and then putting a field back frees up Group, but Having and Execute stay locked until Group itself is touched. The test records that partial recovery deliberately, so it is not mistaken for a flake. It will start FAILING the day the recovery is fixed, and that failure is the signal to flip the expectation - the failure message says so. The defect itself is written up as defect 3 in PaymentStats_Bugs.docx.</t>
+          <t xml:space="preserve">QA 2026-09-15 BillPay: removing every Select chip left 0 chips and the Execute button became disabled. WHY THIS SAYS Automated AND NOT Automated (expected fail), noted 2026-09-24 because the two look contradictory side by side: the test asserts what the panel does TODAY, not what it ought to do, so it passes. Emptying Select and then putting a field back frees up Group, but Having and Execute stay locked until Group itself is touched. The test records that partial recovery deliberately, so it is not mistaken for a flake. It will start FAILING the day the recovery is fixed, and that failure is the signal to flip the expectation - the failure message says so. The defect itself is written up as defect 3 in PaymentStats_Bugs.docx. QA 2026-09-25 REWRITTEN TO THE CASE AS WRITTEN. The test used to assert that Having STAYS disabled after a field is put back into Select - that is the product behaviour, not what this case asks for, so it passed while recording the defect. It now asserts what the Expected Result says: restoring a field re-enables Group, Having and Execute together. Marked test.fail(). Verified on 2026-09-25 - it fails on the Having assertion, which is the defect showing through. Group recovers; Having and Execute only recover once Group is touched as well, the path PS-PQ-06 covers.</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14 SnapPay: left axis ticks read 0,5,10...60 as bare numbers - no ' k' suffix. Confirmed defect. QA 2026-09-25 STATUS CORRECTED to Automated - a test has existed for this since 2026-09-24 and the row still read Not Automated. It covers the LEFT AXIS ONLY. The right-hand axis the case also asks about never renders at all (PT-LOAD-10), so it has no ticks to judge; the test reads whatever axes do paint, so if it is ever wired up its ticks are held to the same rule without further change. The axes are found by SHAPE rather than by content, deliberately: matching on 'looks like a number' would skip the very labels this case is about, since a tick drawn as '20 k' has to be found before it can be judged. Listed as plain Automated rather than expected-fail because, like PS-PQ-05, the test asserts what the panel does today rather than what it ought to do, so it passes now and will start failing the day the suffixes are applied - and its failure message says so. Needs a write-up in the Payment Trends defects document.</t>
+          <t xml:space="preserve">QA 2026-09-14 SnapPay: left axis ticks read 0,5,10...60 as bare numbers - no &amp;#x27; k&amp;#x27; suffix. Confirmed defect. QA 2026-09-25 STATUS CORRECTED to Automated - a test has existed for this since 2026-09-24 and the row still read Not Automated. It covers the LEFT AXIS ONLY. The right-hand axis the case also asks about never renders at all (PT-LOAD-10), so it has no ticks to judge; the test reads whatever axes do paint, so if it is ever wired up its ticks are held to the same rule without further change. The axes are found by SHAPE rather than by content, deliberately: matching on &amp;#x27;looks like a number&amp;#x27; would skip the very labels this case is about, since a tick drawn as &amp;#x27;20 k&amp;#x27; has to be found before it can be judged. Listed as plain Automated rather than expected-fail because, like PS-PQ-05, the test asserts what the panel does today rather than what it ought to do, so it passes now and will start failing the day the suffixes are applied - and its failure message says so. Needs a write-up in the Payment Trends defects document. QA 2026-09-25 REVIEWED AND CLOSED - NOT A DEFECT, closed alongside PT-LOAD-10 for the same reason: unfinished configuration rather than a fault. The left axis counts PAYMENTS. If the ' k' suffix were applied, a month with 20 payments would draw a tick reading '20 k' - twenty thousand. Applying the suffix would make the chart state something false, so fixing it would be worse than leaving it. The only real effect is that a very high-volume merchant reads 50000 rather than 50 k: long, but correct. The test therefore asserts bare numbers as the CORRECT behaviour rather than as a recorded defect; the @knownissue tag has been removed and it is not marked test.fail(). NO WRITE-UP NEEDED - supersedes the earlier note asking for one in the Payment Trends defects document.</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-15 SnapPay: tooltip read Token(3) and Card(52); the summary cards for the same month read Token (3) and Card (52) - identical. AUTOMATED 2026-09-25 on wglUsa, snapPay and paymentus. Measured first rather than reasoned about, by hovering and clicking the SAME bar: wglUsa Ach 43 / Card 80, snapPay Token 19 / Card 92, paymentus Ach 29 / Token 246 / Card 63 - tooltip and cards identical on all three. IPG IS DELIBERATELY EXCLUDED. There the tooltip read Ach 0 / Card 712 while the cards read Ach 0 / Card 0. That mismatch is a real defect but it is already logged twice, as PT-NEG-12 and PT-NEG-13, so running this case on IPG would fail correctly while only re-reporting those. CORRECTION to an earlier analysis: it was claimed the two numbers come from different sources and could legitimately differ, which would have made this case unsound. They agree on three of four gateways, so the case is sound and the earlier reading was wrong. Note for anyone extending it: hoverNewestMonthColumn() takes the newest bar and clickTallestBar() the tallest, so using them together compares two different months. hoverTallestBar() and pressAtPointer() were added to work on one bar.</t>
+          <t xml:space="preserve">QA 2026-09-15 SnapPay: tooltip read Token(3) and Card(52); the summary cards for the same month read Token (3) and Card (52) - identical. AUTOMATED 2026-09-25 on wglUsa, snapPay and paymentus. Measured first rather than reasoned about, by hovering and clicking the SAME bar: wglUsa Ach 43 / Card 80, snapPay Token 19 / Card 92, paymentus Ach 29 / Token 246 / Card 63 - tooltip and cards identical on all three. IPG IS DELIBERATELY EXCLUDED. There the tooltip read Ach 0 / Card 712 while the cards read Ach 0 / Card 0. That mismatch is a real defect but it is already logged twice, as PT-NEG-12 and PT-NEG-13, so running this case on IPG would fail correctly while only re-reporting those. CORRECTION to an earlier analysis: it was claimed the two numbers come from different sources and could legitimately differ, which would have made this case unsound. They agree on three of four gateways, so the case is sound and the earlier reading was wrong. Note for anyone extending it: hoverNewestMonthColumn() takes the newest bar and clickTallestBar() the tallest, so using them together compares two different months. hoverTallestBar() and pressAtPointer() were added to work on one bar. QA 2026-09-25 IPG IS NOW COVERED. The case says all gateways and the test ran only three, leaving the one gateway that disagrees out of the case. IPG has been added and marked test.fail() on its own - the other three stay unmarked so a regression in them still shows. Verified on 2026-09-25: wglUsa, snapPay and paymentus pass, ipg fails as expected. That red run is PT-NEG-12 and PT-NEG-13 showing through, already logged, not a new finding.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -2749,7 +2749,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automated (expected fail)</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-17 IPG, DEFECT CONFIRMED. Every payment_stats_us call carried clientRequestId=1647602068707, the same fixed value on page load and after a date change, exactly as apis/payment.js:101 hard-codes it. Two requests cannot be told apart in logs or traced individually. This is one of only three places in the module where the test reads the network, because the parameter has no UI surface of any kind. RE-CONFIRMED 2026-09-24 on BillPay - the same value 1647602068707, on a different merchant a week later, and on two requests within one session (a 30-day range and a 90-day range) that differed in every other respect. So the value is fixed in the source, not per-session or per-merchant. WHAT THE VALUE TELLS YOU: read as a millisecond timestamp, 1647602068707 is 18 March 2022 11:14:28 UTC - a Date.now() result from one development session pasted in as a constant instead of left as a call. The intent was right; only the call was replaced by its result. Worth checking whether the same literal was pasted elsewhere at the same time, and whether anything downstream has come to rely on it being fixed after four and a half years. Written up as defect 11 in PaymentStats_Bugs.docx, with no screenshots because the parameter has no UI surface.</t>
+          <t xml:space="preserve">QA 2026-09-17 IPG, DEFECT CONFIRMED. Every payment_stats_us call carried clientRequestId=1647602068707, the same fixed value on page load and after a date change, exactly as apis/payment.js:101 hard-codes it. Two requests cannot be told apart in logs or traced individually. This is one of only three places in the module where the test reads the network, because the parameter has no UI surface of any kind. RE-CONFIRMED 2026-09-24 on BillPay - the same value 1647602068707, on a different merchant a week later, and on two requests within one session (a 30-day range and a 90-day range) that differed in every other respect. So the value is fixed in the source, not per-session or per-merchant. WHAT THE VALUE TELLS YOU: read as a millisecond timestamp, 1647602068707 is 18 March 2022 11:14:28 UTC - a Date.now() result from one development session pasted in as a constant instead of left as a call. The intent was right; only the call was replaced by its result. Worth checking whether the same literal was pasted elsewhere at the same time, and whether anything downstream has come to rely on it being fixed after four and a half years. Written up as defect 11 in PaymentStats_Bugs.docx, with no screenshots because the parameter has no UI surface. QA 2026-09-25 NO LONGER EXPECTED-FAIL, by decision - the hard-coded clientRequestId is already written up in the Payment Stats defects document and does not need a second channel, so the test records the behaviour instead of failing on it. It still guards two things: the parameter must be PRESENT on every stats call, and the value must stay the hard-coded 1647602068707. If the identifiers ever start differing per request that is the intended behaviour and the test goes red saying so, with instructions to invert the assertion.</t>
         </is>
       </c>
     </row>

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -7982,7 +7982,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right-hand value axis never renders even though one is configured (known issue)</t>
+          <t xml:space="preserve">Only the left value axis renders; the configured right-hand axis is unused</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Only the left value axis is drawn; the configured right-hand axis never appears, so its fixed 0-110 domain and currency label are dead configuration (defect, log it)</t>
+          <t xml:space="preserve">Only the left value axis is drawn. The configured right-hand axis never appears, so its fixed 0-110 domain and currency label are unused configuration. REVIEWED AND CLOSED on 2026-09-25 - NOT a defect, do not log it. The amounts that axis would have carried are already one click away in the month drill-down.</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value-axis labels render as plain numbers with no ' $' or ' k' suffix (known issue)</t>
+          <t xml:space="preserve">Value-axis labels render as plain numbers with no ' $' or ' k' suffix</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Both axes show bare numbers; the ' k' and ' $' suffixes never render because the label factory discards the symbol (defect, log it)</t>
+          <t xml:space="preserve">Both axes show bare numbers. The ' k' and ' $' suffixes never render because the label factory discards the symbol. REVIEWED AND CLOSED on 2026-09-25 - NOT a defect, do not log it. The left axis counts PAYMENTS, so a tick drawn as '20 k' would claim twenty thousand where there were twenty; applying the suffix would make the chart state something false.</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">

--- a/PaymentAnalytics-TestCases.xlsx
+++ b/PaymentAnalytics-TestCases.xlsx
@@ -8759,7 +8759,7 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA 2026-09-14 SnapPay: 6 months rendered 0 rotated labels, 12 months rendered 12. Boundary holds. AUTOMATED 2026-09-25. Only what was not already covered is asserted; the PT-RANGE-01/02/03 test already walks 3, 12 and 24 months and checks their label counts, the newest label and rotation. Pins the rotation boundary at six. The sibling test proves zero rotation at THREE, which would still pass if the condition were written as &gt;= 6 instead of &gt; 6. Also checks the return leg, 12 back down to 6.</t>
+          <t xml:space="preserve">QA 2026-09-14 SnapPay: 6 months rendered 0 rotated labels, 12 months rendered 12. Boundary holds. AUTOMATED 2026-09-25. Only what was not already covered is asserted; the PT-RANGE-01/02/03 test already walks 3, 12 and 24 months and checks their label counts, the newest label and rotation. Pins the rotation boundary at six. The sibling test proves zero rotation at THREE, which would still pass if the condition were written as &gt;= 6 instead of &gt; 6. Also checks the return leg, 12 back down to 6. QA 2026-09-28 TEST REWRITTEN to walk the case step for step. It previously covered only 6 -&gt; 12 -&gt; 6, which left two gaps: Last 3 Months (step 3) was never checked, and Last 24 Months was never checked at all although the Expected Result names it. It now runs five legs in the case's own order - on load at 6 upright, step 3 at 3 upright, step 4 at 12 slanted, 24 slanted, step 5 back to 6 upright - and each leg is named so a red run says WHICH range broke rather than only reporting a rotation count. Each leg earns its place: 6 is the boundary value (a condition written &gt;= 6 would slant it), 3 guards the other side (a condition written &gt; 3 would pass at 6 and fail there), 12 and 24 stop one rotated range standing in for all of them, and the return leg proves rotation comes OFF again since it is applied by swapping the label component. Verified passing 2026-09-28.</t>
         </is>
       </c>
     </row>
